--- a/data/Data_TK_long.xlsx
+++ b/data/Data_TK_long.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/ew-mix-epximd/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TK/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C79392C5-4E40-C74E-952B-84E969DC1EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B66484-EA08-C545-8CFE-7A854BCD00FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-4080" windowWidth="38400" windowHeight="21100" xr2:uid="{63D67807-0DCA-1F4C-A29E-414A7CCA2C56}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{63D67807-0DCA-1F4C-A29E-414A7CCA2C56}"/>
   </bookViews>
   <sheets>
     <sheet name="TK" sheetId="2" r:id="rId1"/>
@@ -3229,7 +3229,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:17" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
         <v>45439.629166666666</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" s="16">
         <v>45439.629166666666</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="65" spans="1:17" s="3" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>45439.636805555558</v>
       </c>
@@ -8621,7 +8621,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" s="8">
         <v>45460.625</v>
       </c>
@@ -8658,7 +8658,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" s="17">
         <v>45460.625</v>
       </c>
@@ -9028,7 +9028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="193" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A193" s="9">
         <v>45460.625</v>
       </c>
@@ -9845,7 +9845,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" s="8">
         <v>45474.416666666664</v>
       </c>
@@ -9884,7 +9884,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" s="17">
         <v>45474.416666666664</v>
       </c>
@@ -10274,7 +10274,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="225" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A225" s="9">
         <v>45481.416666666664</v>
       </c>
@@ -16342,7 +16342,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="374" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" s="6">
         <v>45475.666666666664</v>
       </c>
@@ -16387,7 +16387,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="375" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" s="6">
         <v>45475.666666666664</v>
       </c>
@@ -16837,7 +16837,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="385" spans="1:17" hidden="1" x14ac:dyDescent="0.2">
+    <row r="385" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A385" s="6">
         <v>45482.690972222219</v>
       </c>
@@ -19766,8 +19766,7 @@
   <autoFilter ref="A1:Q449" xr:uid="{AE06E5C9-F603-BD4A-AB05-F790F7B78C9A}">
     <filterColumn colId="6">
       <filters>
-        <filter val="105"/>
-        <filter val="106"/>
+        <filter val="124"/>
       </filters>
     </filterColumn>
   </autoFilter>

--- a/data/Data_TK_long.xlsx
+++ b/data/Data_TK_long.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TK/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87A30C74-E7C4-214A-960F-F7096825D90C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21381663-6892-6C4E-9AA7-43EFEE8ED752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20" yWindow="760" windowWidth="29400" windowHeight="18380" xr2:uid="{63D67807-0DCA-1F4C-A29E-414A7CCA2C56}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{63D67807-0DCA-1F4C-A29E-414A7CCA2C56}"/>
   </bookViews>
   <sheets>
     <sheet name="TK" sheetId="2" r:id="rId1"/>
     <sheet name="TKBIS_Ctrl" sheetId="3" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TK!$B$1:$R$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TK!$A$1:$R$500</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -452,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -518,13 +518,7 @@
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
@@ -895,113 +889,113 @@
     <col min="15" max="15" width="20.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="44" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:18" s="41" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="44" t="s">
+      <c r="E1" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="44" t="s">
+      <c r="J1" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="N1" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="44" t="s">
+      <c r="O1" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="44" t="s">
+      <c r="P1" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="44" t="s">
+      <c r="Q1" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="44" t="s">
+      <c r="R1" s="41" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:18" s="41" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="B2" s="42">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B2" s="15">
         <v>45439.548611111109</v>
       </c>
-      <c r="C2" s="41">
+      <c r="C2">
         <v>0</v>
       </c>
-      <c r="D2" s="41" t="s">
-        <v>5</v>
-      </c>
-      <c r="E2" s="41">
-        <v>1</v>
-      </c>
-      <c r="F2" s="41">
-        <v>2</v>
-      </c>
-      <c r="G2" s="41" t="s">
+      <c r="D2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>2</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="41">
-        <v>1</v>
-      </c>
-      <c r="I2" s="41">
-        <v>1</v>
-      </c>
-      <c r="J2" s="41">
-        <v>1</v>
-      </c>
-      <c r="K2" s="41">
-        <v>1</v>
-      </c>
-      <c r="L2" s="41" t="s">
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2" t="s">
         <v>7</v>
       </c>
-      <c r="M2" s="41">
+      <c r="M2">
         <v>913</v>
       </c>
-      <c r="N2" s="43"/>
+      <c r="N2" s="17"/>
       <c r="O2" s="18"/>
-      <c r="P2" s="41">
+      <c r="P2">
         <v>1.07</v>
       </c>
-      <c r="R2" s="41" t="s">
+      <c r="R2" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="41" t="s">
+      <c r="A3" t="s">
         <v>30</v>
       </c>
       <c r="B3" s="15">
@@ -1050,7 +1044,7 @@
       </c>
     </row>
     <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="41" t="s">
+      <c r="A4" t="s">
         <v>30</v>
       </c>
       <c r="B4" s="15">
@@ -1098,7 +1092,7 @@
       </c>
     </row>
     <row r="5" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="41" t="s">
+      <c r="A5" t="s">
         <v>30</v>
       </c>
       <c r="B5" s="6">
@@ -1146,7 +1140,7 @@
       </c>
     </row>
     <row r="6" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="41" t="s">
+      <c r="A6" t="s">
         <v>30</v>
       </c>
       <c r="B6" s="5">
@@ -1195,7 +1189,7 @@
       </c>
     </row>
     <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="41" t="s">
+      <c r="A7" t="s">
         <v>30</v>
       </c>
       <c r="B7" s="15">
@@ -1244,7 +1238,7 @@
       </c>
     </row>
     <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="41" t="s">
+      <c r="A8" t="s">
         <v>30</v>
       </c>
       <c r="B8" s="15">
@@ -1292,7 +1286,7 @@
       </c>
     </row>
     <row r="9" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="41" t="s">
+      <c r="A9" t="s">
         <v>30</v>
       </c>
       <c r="B9" s="6">
@@ -1340,7 +1334,7 @@
       </c>
     </row>
     <row r="10" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="41" t="s">
+      <c r="A10" t="s">
         <v>30</v>
       </c>
       <c r="B10" s="5">
@@ -1389,7 +1383,7 @@
       </c>
     </row>
     <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="41" t="s">
+      <c r="A11" t="s">
         <v>30</v>
       </c>
       <c r="B11" s="15">
@@ -1438,7 +1432,7 @@
       </c>
     </row>
     <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="41" t="s">
+      <c r="A12" t="s">
         <v>30</v>
       </c>
       <c r="B12" s="15">
@@ -1486,7 +1480,7 @@
       </c>
     </row>
     <row r="13" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="41" t="s">
+      <c r="A13" t="s">
         <v>30</v>
       </c>
       <c r="B13" s="6">
@@ -1534,7 +1528,7 @@
       </c>
     </row>
     <row r="14" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="41" t="s">
+      <c r="A14" t="s">
         <v>30</v>
       </c>
       <c r="B14" s="5">
@@ -1583,7 +1577,7 @@
       </c>
     </row>
     <row r="15" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="41" t="s">
+      <c r="A15" t="s">
         <v>30</v>
       </c>
       <c r="B15" s="15">
@@ -1632,7 +1626,7 @@
       </c>
     </row>
     <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="41" t="s">
+      <c r="A16" t="s">
         <v>30</v>
       </c>
       <c r="B16" s="15">
@@ -1680,7 +1674,7 @@
       </c>
     </row>
     <row r="17" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="41" t="s">
+      <c r="A17" t="s">
         <v>30</v>
       </c>
       <c r="B17" s="6">
@@ -1728,7 +1722,7 @@
       </c>
     </row>
     <row r="18" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="41" t="s">
+      <c r="A18" t="s">
         <v>30</v>
       </c>
       <c r="B18" s="5">
@@ -1777,7 +1771,7 @@
       </c>
     </row>
     <row r="19" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="41" t="s">
+      <c r="A19" t="s">
         <v>30</v>
       </c>
       <c r="B19" s="15">
@@ -1826,7 +1820,7 @@
       </c>
     </row>
     <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="41" t="s">
+      <c r="A20" t="s">
         <v>30</v>
       </c>
       <c r="B20" s="15">
@@ -1874,7 +1868,7 @@
       </c>
     </row>
     <row r="21" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="41" t="s">
+      <c r="A21" t="s">
         <v>30</v>
       </c>
       <c r="B21" s="6">
@@ -1922,7 +1916,7 @@
       </c>
     </row>
     <row r="22" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="41" t="s">
+      <c r="A22" t="s">
         <v>30</v>
       </c>
       <c r="B22" s="5">
@@ -1971,7 +1965,7 @@
       </c>
     </row>
     <row r="23" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="41" t="s">
+      <c r="A23" t="s">
         <v>30</v>
       </c>
       <c r="B23" s="15">
@@ -2020,7 +2014,7 @@
       </c>
     </row>
     <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="41" t="s">
+      <c r="A24" t="s">
         <v>30</v>
       </c>
       <c r="B24" s="15">
@@ -2068,7 +2062,7 @@
       </c>
     </row>
     <row r="25" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="41" t="s">
+      <c r="A25" t="s">
         <v>30</v>
       </c>
       <c r="B25" s="6">
@@ -2116,7 +2110,7 @@
       </c>
     </row>
     <row r="26" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="41" t="s">
+      <c r="A26" t="s">
         <v>30</v>
       </c>
       <c r="B26" s="5">
@@ -2165,7 +2159,7 @@
       </c>
     </row>
     <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="41" t="s">
+      <c r="A27" t="s">
         <v>30</v>
       </c>
       <c r="B27" s="15">
@@ -2214,7 +2208,7 @@
       </c>
     </row>
     <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="41" t="s">
+      <c r="A28" t="s">
         <v>30</v>
       </c>
       <c r="B28" s="15">
@@ -2262,7 +2256,7 @@
       </c>
     </row>
     <row r="29" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="41" t="s">
+      <c r="A29" t="s">
         <v>30</v>
       </c>
       <c r="B29" s="6">
@@ -2310,7 +2304,7 @@
       </c>
     </row>
     <row r="30" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="41" t="s">
+      <c r="A30" t="s">
         <v>30</v>
       </c>
       <c r="B30" s="5">
@@ -2359,7 +2353,7 @@
       </c>
     </row>
     <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="41" t="s">
+      <c r="A31" t="s">
         <v>30</v>
       </c>
       <c r="B31" s="15">
@@ -2408,7 +2402,7 @@
       </c>
     </row>
     <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="41" t="s">
+      <c r="A32" t="s">
         <v>30</v>
       </c>
       <c r="B32" s="15">
@@ -2456,7 +2450,7 @@
       </c>
     </row>
     <row r="33" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="41" t="s">
+      <c r="A33" t="s">
         <v>30</v>
       </c>
       <c r="B33" s="6">
@@ -2504,7 +2498,7 @@
       </c>
     </row>
     <row r="34" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="41" t="s">
+      <c r="A34" t="s">
         <v>30</v>
       </c>
       <c r="B34" s="5">
@@ -2553,7 +2547,7 @@
       </c>
     </row>
     <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="41" t="s">
+      <c r="A35" t="s">
         <v>30</v>
       </c>
       <c r="B35" s="15">
@@ -2602,7 +2596,7 @@
       </c>
     </row>
     <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="41" t="s">
+      <c r="A36" t="s">
         <v>30</v>
       </c>
       <c r="B36" s="15">
@@ -2650,7 +2644,7 @@
       </c>
     </row>
     <row r="37" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="41" t="s">
+      <c r="A37" t="s">
         <v>30</v>
       </c>
       <c r="B37" s="6">
@@ -2698,7 +2692,7 @@
       </c>
     </row>
     <row r="38" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="41" t="s">
+      <c r="A38" t="s">
         <v>30</v>
       </c>
       <c r="B38" s="5">
@@ -2747,7 +2741,7 @@
       </c>
     </row>
     <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="41" t="s">
+      <c r="A39" t="s">
         <v>30</v>
       </c>
       <c r="B39" s="15">
@@ -2796,7 +2790,7 @@
       </c>
     </row>
     <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="41" t="s">
+      <c r="A40" t="s">
         <v>30</v>
       </c>
       <c r="B40" s="15">
@@ -2844,7 +2838,7 @@
       </c>
     </row>
     <row r="41" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="41" t="s">
+      <c r="A41" t="s">
         <v>30</v>
       </c>
       <c r="B41" s="6">
@@ -2892,7 +2886,7 @@
       </c>
     </row>
     <row r="42" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="41" t="s">
+      <c r="A42" t="s">
         <v>30</v>
       </c>
       <c r="B42" s="5">
@@ -2941,7 +2935,7 @@
       </c>
     </row>
     <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="41" t="s">
+      <c r="A43" t="s">
         <v>30</v>
       </c>
       <c r="B43" s="15">
@@ -2990,7 +2984,7 @@
       </c>
     </row>
     <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="41" t="s">
+      <c r="A44" t="s">
         <v>30</v>
       </c>
       <c r="B44" s="15">
@@ -3038,7 +3032,7 @@
       </c>
     </row>
     <row r="45" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="41" t="s">
+      <c r="A45" t="s">
         <v>30</v>
       </c>
       <c r="B45" s="6">
@@ -3086,7 +3080,7 @@
       </c>
     </row>
     <row r="46" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="41" t="s">
+      <c r="A46" t="s">
         <v>30</v>
       </c>
       <c r="B46" s="5">
@@ -3135,7 +3129,7 @@
       </c>
     </row>
     <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="41" t="s">
+      <c r="A47" t="s">
         <v>30</v>
       </c>
       <c r="B47" s="15">
@@ -3184,7 +3178,7 @@
       </c>
     </row>
     <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="41" t="s">
+      <c r="A48" t="s">
         <v>30</v>
       </c>
       <c r="B48" s="15">
@@ -3232,7 +3226,7 @@
       </c>
     </row>
     <row r="49" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="41" t="s">
+      <c r="A49" t="s">
         <v>30</v>
       </c>
       <c r="B49" s="6">
@@ -3280,7 +3274,7 @@
       </c>
     </row>
     <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="41" t="s">
+      <c r="A50" t="s">
         <v>30</v>
       </c>
       <c r="B50" s="15">
@@ -3329,7 +3323,7 @@
       </c>
     </row>
     <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="41" t="s">
+      <c r="A51" t="s">
         <v>30</v>
       </c>
       <c r="B51" s="15">
@@ -3378,7 +3372,7 @@
       </c>
     </row>
     <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="41" t="s">
+      <c r="A52" t="s">
         <v>30</v>
       </c>
       <c r="B52" s="15">
@@ -3426,7 +3420,7 @@
       </c>
     </row>
     <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="41" t="s">
+      <c r="A53" t="s">
         <v>30</v>
       </c>
       <c r="B53" s="15">
@@ -3474,7 +3468,7 @@
       </c>
     </row>
     <row r="54" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="41" t="s">
+      <c r="A54" t="s">
         <v>30</v>
       </c>
       <c r="B54" s="5">
@@ -3523,7 +3517,7 @@
       </c>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A55" s="41" t="s">
+      <c r="A55" t="s">
         <v>30</v>
       </c>
       <c r="B55" s="15">
@@ -3572,7 +3566,7 @@
       </c>
     </row>
     <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="41" t="s">
+      <c r="A56" t="s">
         <v>30</v>
       </c>
       <c r="B56" s="15">
@@ -3620,7 +3614,7 @@
       </c>
     </row>
     <row r="57" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="41" t="s">
+      <c r="A57" t="s">
         <v>30</v>
       </c>
       <c r="B57" s="6">
@@ -3668,7 +3662,7 @@
       </c>
     </row>
     <row r="58" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="41" t="s">
+      <c r="A58" t="s">
         <v>30</v>
       </c>
       <c r="B58" s="5">
@@ -3717,7 +3711,7 @@
       </c>
     </row>
     <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="41" t="s">
+      <c r="A59" t="s">
         <v>30</v>
       </c>
       <c r="B59" s="15">
@@ -3766,7 +3760,7 @@
       </c>
     </row>
     <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="41" t="s">
+      <c r="A60" t="s">
         <v>30</v>
       </c>
       <c r="B60" s="15">
@@ -3814,7 +3808,7 @@
       </c>
     </row>
     <row r="61" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="41" t="s">
+      <c r="A61" t="s">
         <v>30</v>
       </c>
       <c r="B61" s="6">
@@ -3862,7 +3856,7 @@
       </c>
     </row>
     <row r="62" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="41" t="s">
+      <c r="A62" t="s">
         <v>30</v>
       </c>
       <c r="B62" s="5">
@@ -3911,7 +3905,7 @@
       </c>
     </row>
     <row r="63" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="41" t="s">
+      <c r="A63" t="s">
         <v>30</v>
       </c>
       <c r="B63" s="15">
@@ -3960,7 +3954,7 @@
       </c>
     </row>
     <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="41" t="s">
+      <c r="A64" t="s">
         <v>30</v>
       </c>
       <c r="B64" s="15">
@@ -4008,7 +4002,7 @@
       </c>
     </row>
     <row r="65" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="41" t="s">
+      <c r="A65" t="s">
         <v>30</v>
       </c>
       <c r="B65" s="6">
@@ -4056,7 +4050,7 @@
       </c>
     </row>
     <row r="66" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="41" t="s">
+      <c r="A66" t="s">
         <v>30</v>
       </c>
       <c r="B66" s="5">
@@ -4104,7 +4098,7 @@
       </c>
     </row>
     <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="41" t="s">
+      <c r="A67" t="s">
         <v>30</v>
       </c>
       <c r="B67" s="15">
@@ -4152,7 +4146,7 @@
       </c>
     </row>
     <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="41" t="s">
+      <c r="A68" t="s">
         <v>30</v>
       </c>
       <c r="B68" s="15">
@@ -4199,7 +4193,7 @@
       </c>
     </row>
     <row r="69" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="41" t="s">
+      <c r="A69" t="s">
         <v>30</v>
       </c>
       <c r="B69" s="6">
@@ -4246,7 +4240,7 @@
       </c>
     </row>
     <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="41" t="s">
+      <c r="A70" t="s">
         <v>30</v>
       </c>
       <c r="B70" s="15">
@@ -4294,7 +4288,7 @@
       </c>
     </row>
     <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="41" t="s">
+      <c r="A71" t="s">
         <v>30</v>
       </c>
       <c r="B71" s="15">
@@ -4342,7 +4336,7 @@
       </c>
     </row>
     <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="41" t="s">
+      <c r="A72" t="s">
         <v>30</v>
       </c>
       <c r="B72" s="15">
@@ -4389,7 +4383,7 @@
       </c>
     </row>
     <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="41" t="s">
+      <c r="A73" t="s">
         <v>30</v>
       </c>
       <c r="B73" s="15">
@@ -4436,7 +4430,7 @@
       </c>
     </row>
     <row r="74" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="41" t="s">
+      <c r="A74" t="s">
         <v>30</v>
       </c>
       <c r="B74" s="5">
@@ -4484,7 +4478,7 @@
       </c>
     </row>
     <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="41" t="s">
+      <c r="A75" t="s">
         <v>30</v>
       </c>
       <c r="B75" s="15">
@@ -4532,7 +4526,7 @@
       </c>
     </row>
     <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="41" t="s">
+      <c r="A76" t="s">
         <v>30</v>
       </c>
       <c r="B76" s="15">
@@ -4579,7 +4573,7 @@
       </c>
     </row>
     <row r="77" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="41" t="s">
+      <c r="A77" t="s">
         <v>30</v>
       </c>
       <c r="B77" s="6">
@@ -4626,7 +4620,7 @@
       </c>
     </row>
     <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="41" t="s">
+      <c r="A78" t="s">
         <v>30</v>
       </c>
       <c r="B78" s="15">
@@ -4674,7 +4668,7 @@
       </c>
     </row>
     <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="41" t="s">
+      <c r="A79" t="s">
         <v>30</v>
       </c>
       <c r="B79" s="15">
@@ -4722,7 +4716,7 @@
       </c>
     </row>
     <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="41" t="s">
+      <c r="A80" t="s">
         <v>30</v>
       </c>
       <c r="B80" s="15">
@@ -4769,7 +4763,7 @@
       </c>
     </row>
     <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="41" t="s">
+      <c r="A81" t="s">
         <v>30</v>
       </c>
       <c r="B81" s="15">
@@ -4816,7 +4810,7 @@
       </c>
     </row>
     <row r="82" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="41" t="s">
+      <c r="A82" t="s">
         <v>30</v>
       </c>
       <c r="B82" s="5">
@@ -4864,7 +4858,7 @@
       </c>
     </row>
     <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="41" t="s">
+      <c r="A83" t="s">
         <v>30</v>
       </c>
       <c r="B83" s="15">
@@ -4912,7 +4906,7 @@
       </c>
     </row>
     <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="41" t="s">
+      <c r="A84" t="s">
         <v>30</v>
       </c>
       <c r="B84" s="15">
@@ -4959,7 +4953,7 @@
       </c>
     </row>
     <row r="85" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="41" t="s">
+      <c r="A85" t="s">
         <v>30</v>
       </c>
       <c r="B85" s="6">
@@ -5006,7 +5000,7 @@
       </c>
     </row>
     <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="41" t="s">
+      <c r="A86" t="s">
         <v>30</v>
       </c>
       <c r="B86" s="15">
@@ -5054,7 +5048,7 @@
       </c>
     </row>
     <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="41" t="s">
+      <c r="A87" t="s">
         <v>30</v>
       </c>
       <c r="B87" s="15">
@@ -5102,7 +5096,7 @@
       </c>
     </row>
     <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="41" t="s">
+      <c r="A88" t="s">
         <v>30</v>
       </c>
       <c r="B88" s="15">
@@ -5149,7 +5143,7 @@
       </c>
     </row>
     <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="41" t="s">
+      <c r="A89" t="s">
         <v>30</v>
       </c>
       <c r="B89" s="15">
@@ -5196,7 +5190,7 @@
       </c>
     </row>
     <row r="90" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="41" t="s">
+      <c r="A90" t="s">
         <v>30</v>
       </c>
       <c r="B90" s="5">
@@ -5243,8 +5237,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="41" t="s">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
         <v>30</v>
       </c>
       <c r="B91" s="15">
@@ -5288,11 +5282,11 @@
         <v>8.8999999999999996E-2</v>
       </c>
       <c r="R91" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="41" t="s">
+      <c r="A92" t="s">
         <v>30</v>
       </c>
       <c r="B92" s="15">
@@ -5339,7 +5333,7 @@
       </c>
     </row>
     <row r="93" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="41" t="s">
+      <c r="A93" t="s">
         <v>30</v>
       </c>
       <c r="B93" s="6">
@@ -5386,7 +5380,7 @@
       </c>
     </row>
     <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="41" t="s">
+      <c r="A94" t="s">
         <v>30</v>
       </c>
       <c r="B94" s="15">
@@ -5434,7 +5428,7 @@
       </c>
     </row>
     <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="41" t="s">
+      <c r="A95" t="s">
         <v>30</v>
       </c>
       <c r="B95" s="15">
@@ -5482,7 +5476,7 @@
       </c>
     </row>
     <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="41" t="s">
+      <c r="A96" t="s">
         <v>30</v>
       </c>
       <c r="B96" s="15">
@@ -5529,7 +5523,7 @@
       </c>
     </row>
     <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="41" t="s">
+      <c r="A97" t="s">
         <v>30</v>
       </c>
       <c r="B97" s="15">
@@ -5576,7 +5570,7 @@
       </c>
     </row>
     <row r="98" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="41" t="s">
+      <c r="A98" t="s">
         <v>30</v>
       </c>
       <c r="B98" s="5">
@@ -5624,7 +5618,7 @@
       </c>
     </row>
     <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="41" t="s">
+      <c r="A99" t="s">
         <v>30</v>
       </c>
       <c r="B99" s="15">
@@ -5672,7 +5666,7 @@
       </c>
     </row>
     <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="41" t="s">
+      <c r="A100" t="s">
         <v>30</v>
       </c>
       <c r="B100" s="15">
@@ -5719,7 +5713,7 @@
       </c>
     </row>
     <row r="101" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="41" t="s">
+      <c r="A101" t="s">
         <v>30</v>
       </c>
       <c r="B101" s="6">
@@ -5766,7 +5760,7 @@
       </c>
     </row>
     <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="41" t="s">
+      <c r="A102" t="s">
         <v>30</v>
       </c>
       <c r="B102" s="15">
@@ -5814,7 +5808,7 @@
       </c>
     </row>
     <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="41" t="s">
+      <c r="A103" t="s">
         <v>30</v>
       </c>
       <c r="B103" s="15">
@@ -5862,7 +5856,7 @@
       </c>
     </row>
     <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="41" t="s">
+      <c r="A104" t="s">
         <v>30</v>
       </c>
       <c r="B104" s="15">
@@ -5909,7 +5903,7 @@
       </c>
     </row>
     <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="41" t="s">
+      <c r="A105" t="s">
         <v>30</v>
       </c>
       <c r="B105" s="15">
@@ -5956,7 +5950,7 @@
       </c>
     </row>
     <row r="106" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="41" t="s">
+      <c r="A106" t="s">
         <v>30</v>
       </c>
       <c r="B106" s="5">
@@ -6004,7 +5998,7 @@
       </c>
     </row>
     <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="41" t="s">
+      <c r="A107" t="s">
         <v>30</v>
       </c>
       <c r="B107" s="15">
@@ -6052,7 +6046,7 @@
       </c>
     </row>
     <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="41" t="s">
+      <c r="A108" t="s">
         <v>30</v>
       </c>
       <c r="B108" s="15">
@@ -6099,7 +6093,7 @@
       </c>
     </row>
     <row r="109" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="41" t="s">
+      <c r="A109" t="s">
         <v>30</v>
       </c>
       <c r="B109" s="6">
@@ -6146,7 +6140,7 @@
       </c>
     </row>
     <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="41" t="s">
+      <c r="A110" t="s">
         <v>30</v>
       </c>
       <c r="B110" s="15">
@@ -6194,7 +6188,7 @@
       </c>
     </row>
     <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A111" s="41" t="s">
+      <c r="A111" t="s">
         <v>30</v>
       </c>
       <c r="B111" s="15">
@@ -6242,7 +6236,7 @@
       </c>
     </row>
     <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A112" s="41" t="s">
+      <c r="A112" t="s">
         <v>30</v>
       </c>
       <c r="B112" s="15">
@@ -6289,7 +6283,7 @@
       </c>
     </row>
     <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A113" s="41" t="s">
+      <c r="A113" t="s">
         <v>30</v>
       </c>
       <c r="B113" s="15">
@@ -6336,7 +6330,7 @@
       </c>
     </row>
     <row r="114" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A114" s="41" t="s">
+      <c r="A114" t="s">
         <v>30</v>
       </c>
       <c r="B114" s="5">
@@ -6384,7 +6378,7 @@
       </c>
     </row>
     <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A115" s="41" t="s">
+      <c r="A115" t="s">
         <v>30</v>
       </c>
       <c r="B115" s="15">
@@ -6432,7 +6426,7 @@
       </c>
     </row>
     <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A116" s="41" t="s">
+      <c r="A116" t="s">
         <v>30</v>
       </c>
       <c r="B116" s="15">
@@ -6479,7 +6473,7 @@
       </c>
     </row>
     <row r="117" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A117" s="41" t="s">
+      <c r="A117" t="s">
         <v>30</v>
       </c>
       <c r="B117" s="6">
@@ -6526,7 +6520,7 @@
       </c>
     </row>
     <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A118" s="41" t="s">
+      <c r="A118" t="s">
         <v>30</v>
       </c>
       <c r="B118" s="15">
@@ -6574,7 +6568,7 @@
       </c>
     </row>
     <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A119" s="41" t="s">
+      <c r="A119" t="s">
         <v>30</v>
       </c>
       <c r="B119" s="15">
@@ -6622,7 +6616,7 @@
       </c>
     </row>
     <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A120" s="41" t="s">
+      <c r="A120" t="s">
         <v>30</v>
       </c>
       <c r="B120" s="15">
@@ -6669,7 +6663,7 @@
       </c>
     </row>
     <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A121" s="41" t="s">
+      <c r="A121" t="s">
         <v>30</v>
       </c>
       <c r="B121" s="15">
@@ -6716,7 +6710,7 @@
       </c>
     </row>
     <row r="122" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A122" s="41" t="s">
+      <c r="A122" t="s">
         <v>30</v>
       </c>
       <c r="B122" s="5">
@@ -6764,7 +6758,7 @@
       </c>
     </row>
     <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A123" s="41" t="s">
+      <c r="A123" t="s">
         <v>30</v>
       </c>
       <c r="B123" s="15">
@@ -6812,7 +6806,7 @@
       </c>
     </row>
     <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A124" s="41" t="s">
+      <c r="A124" t="s">
         <v>30</v>
       </c>
       <c r="B124" s="15">
@@ -6859,7 +6853,7 @@
       </c>
     </row>
     <row r="125" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A125" s="41" t="s">
+      <c r="A125" t="s">
         <v>30</v>
       </c>
       <c r="B125" s="6">
@@ -6906,7 +6900,7 @@
       </c>
     </row>
     <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A126" s="41" t="s">
+      <c r="A126" t="s">
         <v>30</v>
       </c>
       <c r="B126" s="15">
@@ -6954,7 +6948,7 @@
       </c>
     </row>
     <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A127" s="41" t="s">
+      <c r="A127" t="s">
         <v>30</v>
       </c>
       <c r="B127" s="15">
@@ -7002,7 +6996,7 @@
       </c>
     </row>
     <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A128" s="41" t="s">
+      <c r="A128" t="s">
         <v>30</v>
       </c>
       <c r="B128" s="15">
@@ -7049,7 +7043,7 @@
       </c>
     </row>
     <row r="129" spans="1:18" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="41" t="s">
+      <c r="A129" t="s">
         <v>30</v>
       </c>
       <c r="B129" s="28">
@@ -7097,7 +7091,7 @@
       </c>
     </row>
     <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A130" s="41" t="s">
+      <c r="A130" t="s">
         <v>30</v>
       </c>
       <c r="B130" s="11">
@@ -7139,7 +7133,7 @@
       </c>
     </row>
     <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A131" s="41" t="s">
+      <c r="A131" t="s">
         <v>30</v>
       </c>
       <c r="B131" s="16">
@@ -7181,7 +7175,7 @@
       </c>
     </row>
     <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A132" s="41" t="s">
+      <c r="A132" t="s">
         <v>30</v>
       </c>
       <c r="B132" s="16">
@@ -7223,7 +7217,7 @@
       </c>
     </row>
     <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A133" s="41" t="s">
+      <c r="A133" t="s">
         <v>30</v>
       </c>
       <c r="B133" s="8">
@@ -7265,7 +7259,7 @@
       </c>
     </row>
     <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A134" s="41" t="s">
+      <c r="A134" t="s">
         <v>30</v>
       </c>
       <c r="B134" s="7">
@@ -7307,7 +7301,7 @@
       </c>
     </row>
     <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A135" s="41" t="s">
+      <c r="A135" t="s">
         <v>30</v>
       </c>
       <c r="B135" s="16">
@@ -7349,7 +7343,7 @@
       </c>
     </row>
     <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A136" s="41" t="s">
+      <c r="A136" t="s">
         <v>30</v>
       </c>
       <c r="B136" s="16">
@@ -7391,7 +7385,7 @@
       </c>
     </row>
     <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A137" s="41" t="s">
+      <c r="A137" t="s">
         <v>30</v>
       </c>
       <c r="B137" s="8">
@@ -7433,7 +7427,7 @@
       </c>
     </row>
     <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A138" s="41" t="s">
+      <c r="A138" t="s">
         <v>30</v>
       </c>
       <c r="B138" s="7">
@@ -7475,7 +7469,7 @@
       </c>
     </row>
     <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A139" s="41" t="s">
+      <c r="A139" t="s">
         <v>30</v>
       </c>
       <c r="B139" s="16">
@@ -7517,7 +7511,7 @@
       </c>
     </row>
     <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A140" s="41" t="s">
+      <c r="A140" t="s">
         <v>30</v>
       </c>
       <c r="B140" s="16">
@@ -7559,7 +7553,7 @@
       </c>
     </row>
     <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A141" s="41" t="s">
+      <c r="A141" t="s">
         <v>30</v>
       </c>
       <c r="B141" s="8">
@@ -7601,7 +7595,7 @@
       </c>
     </row>
     <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A142" s="41" t="s">
+      <c r="A142" t="s">
         <v>30</v>
       </c>
       <c r="B142" s="7">
@@ -7646,7 +7640,7 @@
       </c>
     </row>
     <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A143" s="41" t="s">
+      <c r="A143" t="s">
         <v>30</v>
       </c>
       <c r="B143" s="16">
@@ -7688,7 +7682,7 @@
       </c>
     </row>
     <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A144" s="41" t="s">
+      <c r="A144" t="s">
         <v>30</v>
       </c>
       <c r="B144" s="16">
@@ -7730,7 +7724,7 @@
       </c>
     </row>
     <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A145" s="41" t="s">
+      <c r="A145" t="s">
         <v>30</v>
       </c>
       <c r="B145" s="8">
@@ -7772,7 +7766,7 @@
       </c>
     </row>
     <row r="146" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A146" s="41" t="s">
+      <c r="A146" t="s">
         <v>30</v>
       </c>
       <c r="B146" s="7">
@@ -7814,7 +7808,7 @@
       </c>
     </row>
     <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A147" s="41" t="s">
+      <c r="A147" t="s">
         <v>30</v>
       </c>
       <c r="B147" s="16">
@@ -7856,7 +7850,7 @@
       </c>
     </row>
     <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A148" s="41" t="s">
+      <c r="A148" t="s">
         <v>30</v>
       </c>
       <c r="B148" s="16">
@@ -7898,7 +7892,7 @@
       </c>
     </row>
     <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A149" s="41" t="s">
+      <c r="A149" t="s">
         <v>30</v>
       </c>
       <c r="B149" s="8">
@@ -7940,7 +7934,7 @@
       </c>
     </row>
     <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A150" s="41" t="s">
+      <c r="A150" t="s">
         <v>30</v>
       </c>
       <c r="B150" s="7">
@@ -7985,7 +7979,7 @@
       </c>
     </row>
     <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A151" s="41" t="s">
+      <c r="A151" t="s">
         <v>30</v>
       </c>
       <c r="B151" s="16">
@@ -8027,7 +8021,7 @@
       </c>
     </row>
     <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A152" s="41" t="s">
+      <c r="A152" t="s">
         <v>30</v>
       </c>
       <c r="B152" s="16">
@@ -8069,7 +8063,7 @@
       </c>
     </row>
     <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A153" s="41" t="s">
+      <c r="A153" t="s">
         <v>30</v>
       </c>
       <c r="B153" s="8">
@@ -8111,7 +8105,7 @@
       </c>
     </row>
     <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A154" s="41" t="s">
+      <c r="A154" t="s">
         <v>30</v>
       </c>
       <c r="B154" s="7">
@@ -8153,7 +8147,7 @@
       </c>
     </row>
     <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A155" s="41" t="s">
+      <c r="A155" t="s">
         <v>30</v>
       </c>
       <c r="B155" s="16">
@@ -8195,7 +8189,7 @@
       </c>
     </row>
     <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A156" s="41" t="s">
+      <c r="A156" t="s">
         <v>30</v>
       </c>
       <c r="B156" s="16">
@@ -8237,7 +8231,7 @@
       </c>
     </row>
     <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="41" t="s">
+      <c r="A157" t="s">
         <v>30</v>
       </c>
       <c r="B157" s="8">
@@ -8279,7 +8273,7 @@
       </c>
     </row>
     <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="41" t="s">
+      <c r="A158" t="s">
         <v>30</v>
       </c>
       <c r="B158" s="7">
@@ -8321,7 +8315,7 @@
       </c>
     </row>
     <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="41" t="s">
+      <c r="A159" t="s">
         <v>30</v>
       </c>
       <c r="B159" s="16">
@@ -8363,7 +8357,7 @@
       </c>
     </row>
     <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="41" t="s">
+      <c r="A160" t="s">
         <v>30</v>
       </c>
       <c r="B160" s="16">
@@ -8405,7 +8399,7 @@
       </c>
     </row>
     <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="41" t="s">
+      <c r="A161" t="s">
         <v>30</v>
       </c>
       <c r="B161" s="8">
@@ -8450,7 +8444,7 @@
       </c>
     </row>
     <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A162" s="41" t="s">
+      <c r="A162" t="s">
         <v>30</v>
       </c>
       <c r="B162" s="7">
@@ -8490,7 +8484,7 @@
       </c>
     </row>
     <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A163" s="41" t="s">
+      <c r="A163" t="s">
         <v>30</v>
       </c>
       <c r="B163" s="16">
@@ -8530,7 +8524,7 @@
       </c>
     </row>
     <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="41" t="s">
+      <c r="A164" t="s">
         <v>30</v>
       </c>
       <c r="B164" s="16">
@@ -8570,7 +8564,7 @@
       </c>
     </row>
     <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="41" t="s">
+      <c r="A165" t="s">
         <v>30</v>
       </c>
       <c r="B165" s="8">
@@ -8610,7 +8604,7 @@
       </c>
     </row>
     <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="41" t="s">
+      <c r="A166" t="s">
         <v>30</v>
       </c>
       <c r="B166" s="7">
@@ -8650,7 +8644,7 @@
       </c>
     </row>
     <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="41" t="s">
+      <c r="A167" t="s">
         <v>30</v>
       </c>
       <c r="B167" s="16">
@@ -8690,7 +8684,7 @@
       </c>
     </row>
     <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="41" t="s">
+      <c r="A168" t="s">
         <v>30</v>
       </c>
       <c r="B168" s="16">
@@ -8730,7 +8724,7 @@
       </c>
     </row>
     <row r="169" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="41" t="s">
+      <c r="A169" t="s">
         <v>30</v>
       </c>
       <c r="B169" s="8">
@@ -8770,7 +8764,7 @@
       </c>
     </row>
     <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A170" s="41" t="s">
+      <c r="A170" t="s">
         <v>30</v>
       </c>
       <c r="B170" s="7">
@@ -8810,7 +8804,7 @@
       </c>
     </row>
     <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A171" s="41" t="s">
+      <c r="A171" t="s">
         <v>30</v>
       </c>
       <c r="B171" s="16">
@@ -8850,7 +8844,7 @@
       </c>
     </row>
     <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A172" s="41" t="s">
+      <c r="A172" t="s">
         <v>30</v>
       </c>
       <c r="B172" s="16">
@@ -8890,7 +8884,7 @@
       </c>
     </row>
     <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A173" s="41" t="s">
+      <c r="A173" t="s">
         <v>30</v>
       </c>
       <c r="B173" s="8">
@@ -8930,7 +8924,7 @@
       </c>
     </row>
     <row r="174" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A174" s="41" t="s">
+      <c r="A174" t="s">
         <v>30</v>
       </c>
       <c r="B174" s="7">
@@ -8970,7 +8964,7 @@
       </c>
     </row>
     <row r="175" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A175" s="41" t="s">
+      <c r="A175" t="s">
         <v>30</v>
       </c>
       <c r="B175" s="16">
@@ -9010,7 +9004,7 @@
       </c>
     </row>
     <row r="176" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A176" s="41" t="s">
+      <c r="A176" t="s">
         <v>30</v>
       </c>
       <c r="B176" s="16">
@@ -9050,7 +9044,7 @@
       </c>
     </row>
     <row r="177" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A177" s="41" t="s">
+      <c r="A177" t="s">
         <v>30</v>
       </c>
       <c r="B177" s="8">
@@ -9090,7 +9084,7 @@
       </c>
     </row>
     <row r="178" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A178" s="41" t="s">
+      <c r="A178" t="s">
         <v>30</v>
       </c>
       <c r="B178" s="7">
@@ -9130,7 +9124,7 @@
       </c>
     </row>
     <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A179" s="41" t="s">
+      <c r="A179" t="s">
         <v>30</v>
       </c>
       <c r="B179" s="16">
@@ -9170,7 +9164,7 @@
       </c>
     </row>
     <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A180" s="41" t="s">
+      <c r="A180" t="s">
         <v>30</v>
       </c>
       <c r="B180" s="16">
@@ -9210,7 +9204,7 @@
       </c>
     </row>
     <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A181" s="41" t="s">
+      <c r="A181" t="s">
         <v>30</v>
       </c>
       <c r="B181" s="8">
@@ -9250,7 +9244,7 @@
       </c>
     </row>
     <row r="182" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A182" s="41" t="s">
+      <c r="A182" t="s">
         <v>30</v>
       </c>
       <c r="B182" s="7">
@@ -9290,7 +9284,7 @@
       </c>
     </row>
     <row r="183" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A183" s="41" t="s">
+      <c r="A183" t="s">
         <v>30</v>
       </c>
       <c r="B183" s="16">
@@ -9330,7 +9324,7 @@
       </c>
     </row>
     <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A184" s="41" t="s">
+      <c r="A184" t="s">
         <v>30</v>
       </c>
       <c r="B184" s="16">
@@ -9370,7 +9364,7 @@
       </c>
     </row>
     <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A185" s="41" t="s">
+      <c r="A185" t="s">
         <v>30</v>
       </c>
       <c r="B185" s="8">
@@ -9410,7 +9404,7 @@
       </c>
     </row>
     <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A186" s="41" t="s">
+      <c r="A186" t="s">
         <v>30</v>
       </c>
       <c r="B186" s="7">
@@ -9450,7 +9444,7 @@
       </c>
     </row>
     <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A187" s="41" t="s">
+      <c r="A187" t="s">
         <v>30</v>
       </c>
       <c r="B187" s="16">
@@ -9490,7 +9484,7 @@
       </c>
     </row>
     <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A188" s="41" t="s">
+      <c r="A188" t="s">
         <v>30</v>
       </c>
       <c r="B188" s="16">
@@ -9530,7 +9524,7 @@
       </c>
     </row>
     <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A189" s="41" t="s">
+      <c r="A189" t="s">
         <v>30</v>
       </c>
       <c r="B189" s="8">
@@ -9570,7 +9564,7 @@
       </c>
     </row>
     <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A190" s="41" t="s">
+      <c r="A190" t="s">
         <v>30</v>
       </c>
       <c r="B190" s="7">
@@ -9610,7 +9604,7 @@
       </c>
     </row>
     <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A191" s="41" t="s">
+      <c r="A191" t="s">
         <v>30</v>
       </c>
       <c r="B191" s="16">
@@ -9650,7 +9644,7 @@
       </c>
     </row>
     <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A192" s="41" t="s">
+      <c r="A192" t="s">
         <v>30</v>
       </c>
       <c r="B192" s="16">
@@ -9690,7 +9684,7 @@
       </c>
     </row>
     <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A193" s="41" t="s">
+      <c r="A193" t="s">
         <v>30</v>
       </c>
       <c r="B193" s="8">
@@ -9730,7 +9724,7 @@
       </c>
     </row>
     <row r="194" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A194" s="41" t="s">
+      <c r="A194" t="s">
         <v>30</v>
       </c>
       <c r="B194" s="7">
@@ -9772,7 +9766,7 @@
       </c>
     </row>
     <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A195" s="41" t="s">
+      <c r="A195" t="s">
         <v>30</v>
       </c>
       <c r="B195" s="16">
@@ -9814,7 +9808,7 @@
       </c>
     </row>
     <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A196" s="41" t="s">
+      <c r="A196" t="s">
         <v>30</v>
       </c>
       <c r="B196" s="16">
@@ -9856,7 +9850,7 @@
       </c>
     </row>
     <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A197" s="41" t="s">
+      <c r="A197" t="s">
         <v>30</v>
       </c>
       <c r="B197" s="8">
@@ -9898,7 +9892,7 @@
       </c>
     </row>
     <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A198" s="41" t="s">
+      <c r="A198" t="s">
         <v>30</v>
       </c>
       <c r="B198" s="7">
@@ -9940,7 +9934,7 @@
       </c>
     </row>
     <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A199" s="41" t="s">
+      <c r="A199" t="s">
         <v>30</v>
       </c>
       <c r="B199" s="16">
@@ -9982,7 +9976,7 @@
       </c>
     </row>
     <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A200" s="41" t="s">
+      <c r="A200" t="s">
         <v>30</v>
       </c>
       <c r="B200" s="16">
@@ -10024,7 +10018,7 @@
       </c>
     </row>
     <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A201" s="41" t="s">
+      <c r="A201" t="s">
         <v>30</v>
       </c>
       <c r="B201" s="8">
@@ -10066,7 +10060,7 @@
       </c>
     </row>
     <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A202" s="41" t="s">
+      <c r="A202" t="s">
         <v>30</v>
       </c>
       <c r="B202" s="7">
@@ -10108,7 +10102,7 @@
       </c>
     </row>
     <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A203" s="41" t="s">
+      <c r="A203" t="s">
         <v>30</v>
       </c>
       <c r="B203" s="16">
@@ -10150,7 +10144,7 @@
       </c>
     </row>
     <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A204" s="41" t="s">
+      <c r="A204" t="s">
         <v>30</v>
       </c>
       <c r="B204" s="16">
@@ -10192,7 +10186,7 @@
       </c>
     </row>
     <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A205" s="41" t="s">
+      <c r="A205" t="s">
         <v>30</v>
       </c>
       <c r="B205" s="8">
@@ -10234,7 +10228,7 @@
       </c>
     </row>
     <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A206" s="41" t="s">
+      <c r="A206" t="s">
         <v>30</v>
       </c>
       <c r="B206" s="7">
@@ -10276,7 +10270,7 @@
       </c>
     </row>
     <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A207" s="41" t="s">
+      <c r="A207" t="s">
         <v>30</v>
       </c>
       <c r="B207" s="16">
@@ -10318,7 +10312,7 @@
       </c>
     </row>
     <row r="208" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A208" s="41" t="s">
+      <c r="A208" t="s">
         <v>30</v>
       </c>
       <c r="B208" s="16">
@@ -10360,7 +10354,7 @@
       </c>
     </row>
     <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A209" s="41" t="s">
+      <c r="A209" t="s">
         <v>30</v>
       </c>
       <c r="B209" s="8">
@@ -10402,7 +10396,7 @@
       </c>
     </row>
     <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A210" s="41" t="s">
+      <c r="A210" t="s">
         <v>30</v>
       </c>
       <c r="B210" s="16">
@@ -10444,7 +10438,7 @@
       </c>
     </row>
     <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A211" s="41" t="s">
+      <c r="A211" t="s">
         <v>30</v>
       </c>
       <c r="B211" s="16">
@@ -10486,7 +10480,7 @@
       </c>
     </row>
     <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A212" s="41" t="s">
+      <c r="A212" t="s">
         <v>30</v>
       </c>
       <c r="B212" s="16">
@@ -10528,7 +10522,7 @@
       </c>
     </row>
     <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A213" s="41" t="s">
+      <c r="A213" t="s">
         <v>30</v>
       </c>
       <c r="B213" s="16">
@@ -10570,7 +10564,7 @@
       </c>
     </row>
     <row r="214" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A214" s="41" t="s">
+      <c r="A214" t="s">
         <v>30</v>
       </c>
       <c r="B214" s="7">
@@ -10612,7 +10606,7 @@
       </c>
     </row>
     <row r="215" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A215" s="41" t="s">
+      <c r="A215" t="s">
         <v>30</v>
       </c>
       <c r="B215" s="16">
@@ -10654,7 +10648,7 @@
       </c>
     </row>
     <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A216" s="41" t="s">
+      <c r="A216" t="s">
         <v>30</v>
       </c>
       <c r="B216" s="16">
@@ -10696,7 +10690,7 @@
       </c>
     </row>
     <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A217" s="41" t="s">
+      <c r="A217" t="s">
         <v>30</v>
       </c>
       <c r="B217" s="8">
@@ -10738,7 +10732,7 @@
       </c>
     </row>
     <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A218" s="41" t="s">
+      <c r="A218" t="s">
         <v>30</v>
       </c>
       <c r="B218" s="7">
@@ -10780,7 +10774,7 @@
       </c>
     </row>
     <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A219" s="41" t="s">
+      <c r="A219" t="s">
         <v>30</v>
       </c>
       <c r="B219" s="16">
@@ -10822,7 +10816,7 @@
       </c>
     </row>
     <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A220" s="41" t="s">
+      <c r="A220" t="s">
         <v>30</v>
       </c>
       <c r="B220" s="16">
@@ -10864,7 +10858,7 @@
       </c>
     </row>
     <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A221" s="41" t="s">
+      <c r="A221" t="s">
         <v>30</v>
       </c>
       <c r="B221" s="8">
@@ -10906,7 +10900,7 @@
       </c>
     </row>
     <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A222" s="41" t="s">
+      <c r="A222" t="s">
         <v>30</v>
       </c>
       <c r="B222" s="7">
@@ -10948,7 +10942,7 @@
       </c>
     </row>
     <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A223" s="41" t="s">
+      <c r="A223" t="s">
         <v>30</v>
       </c>
       <c r="B223" s="16">
@@ -10990,7 +10984,7 @@
       </c>
     </row>
     <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A224" s="41" t="s">
+      <c r="A224" t="s">
         <v>30</v>
       </c>
       <c r="B224" s="16">
@@ -11032,7 +11026,7 @@
       </c>
     </row>
     <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A225" s="41" t="s">
+      <c r="A225" t="s">
         <v>30</v>
       </c>
       <c r="B225" s="8">
@@ -11074,7 +11068,7 @@
       </c>
     </row>
     <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A226" s="41" t="s">
+      <c r="A226" t="s">
         <v>30</v>
       </c>
       <c r="B226" s="7">
@@ -11116,7 +11110,7 @@
       </c>
     </row>
     <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A227" s="41" t="s">
+      <c r="A227" t="s">
         <v>30</v>
       </c>
       <c r="B227" s="16">
@@ -11158,7 +11152,7 @@
       </c>
     </row>
     <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A228" s="41" t="s">
+      <c r="A228" t="s">
         <v>30</v>
       </c>
       <c r="B228" s="16">
@@ -11200,7 +11194,7 @@
       </c>
     </row>
     <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A229" s="41" t="s">
+      <c r="A229" t="s">
         <v>30</v>
       </c>
       <c r="B229" s="8">
@@ -11242,7 +11236,7 @@
       </c>
     </row>
     <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A230" s="41" t="s">
+      <c r="A230" t="s">
         <v>30</v>
       </c>
       <c r="B230" s="16">
@@ -11284,7 +11278,7 @@
       </c>
     </row>
     <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A231" s="41" t="s">
+      <c r="A231" t="s">
         <v>30</v>
       </c>
       <c r="B231" s="16">
@@ -11326,7 +11320,7 @@
       </c>
     </row>
     <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A232" s="41" t="s">
+      <c r="A232" t="s">
         <v>30</v>
       </c>
       <c r="B232" s="16">
@@ -11368,7 +11362,7 @@
       </c>
     </row>
     <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A233" s="41" t="s">
+      <c r="A233" t="s">
         <v>30</v>
       </c>
       <c r="B233" s="16">
@@ -11410,7 +11404,7 @@
       </c>
     </row>
     <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A234" s="41" t="s">
+      <c r="A234" t="s">
         <v>30</v>
       </c>
       <c r="B234" s="7">
@@ -11452,7 +11446,7 @@
       </c>
     </row>
     <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A235" s="41" t="s">
+      <c r="A235" t="s">
         <v>30</v>
       </c>
       <c r="B235" s="16">
@@ -11494,7 +11488,7 @@
       </c>
     </row>
     <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A236" s="41" t="s">
+      <c r="A236" t="s">
         <v>30</v>
       </c>
       <c r="B236" s="16">
@@ -11536,7 +11530,7 @@
       </c>
     </row>
     <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A237" s="41" t="s">
+      <c r="A237" t="s">
         <v>30</v>
       </c>
       <c r="B237" s="8">
@@ -11578,7 +11572,7 @@
       </c>
     </row>
     <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A238" s="41" t="s">
+      <c r="A238" t="s">
         <v>30</v>
       </c>
       <c r="B238" s="16">
@@ -11620,7 +11614,7 @@
       </c>
     </row>
     <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A239" s="41" t="s">
+      <c r="A239" t="s">
         <v>30</v>
       </c>
       <c r="B239" s="16">
@@ -11662,7 +11656,7 @@
       </c>
     </row>
     <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A240" s="41" t="s">
+      <c r="A240" t="s">
         <v>30</v>
       </c>
       <c r="B240" s="16">
@@ -11704,7 +11698,7 @@
       </c>
     </row>
     <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A241" s="41" t="s">
+      <c r="A241" t="s">
         <v>30</v>
       </c>
       <c r="B241" s="16">
@@ -11749,7 +11743,7 @@
       </c>
     </row>
     <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A242" s="41" t="s">
+      <c r="A242" t="s">
         <v>30</v>
       </c>
       <c r="B242" s="7">
@@ -11791,7 +11785,7 @@
       </c>
     </row>
     <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A243" s="41" t="s">
+      <c r="A243" t="s">
         <v>30</v>
       </c>
       <c r="B243" s="16">
@@ -11833,7 +11827,7 @@
       </c>
     </row>
     <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A244" s="41" t="s">
+      <c r="A244" t="s">
         <v>30</v>
       </c>
       <c r="B244" s="16">
@@ -11875,7 +11869,7 @@
       </c>
     </row>
     <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A245" s="41" t="s">
+      <c r="A245" t="s">
         <v>30</v>
       </c>
       <c r="B245" s="8">
@@ -11917,7 +11911,7 @@
       </c>
     </row>
     <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A246" s="41" t="s">
+      <c r="A246" t="s">
         <v>30</v>
       </c>
       <c r="B246" s="16">
@@ -11959,7 +11953,7 @@
       </c>
     </row>
     <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A247" s="41" t="s">
+      <c r="A247" t="s">
         <v>30</v>
       </c>
       <c r="B247" s="16">
@@ -12001,7 +11995,7 @@
       </c>
     </row>
     <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A248" s="41" t="s">
+      <c r="A248" t="s">
         <v>30</v>
       </c>
       <c r="B248" s="16">
@@ -12043,7 +12037,7 @@
       </c>
     </row>
     <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A249" s="41" t="s">
+      <c r="A249" t="s">
         <v>30</v>
       </c>
       <c r="B249" s="16">
@@ -12088,7 +12082,7 @@
       </c>
     </row>
     <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A250" s="41" t="s">
+      <c r="A250" t="s">
         <v>30</v>
       </c>
       <c r="B250" s="7">
@@ -12129,8 +12123,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A251" s="41" t="s">
+    <row r="251" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A251" t="s">
         <v>30</v>
       </c>
       <c r="B251" s="16">
@@ -12168,11 +12162,11 @@
         <v>786.3</v>
       </c>
       <c r="R251" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A252" s="41" t="s">
+      <c r="A252" t="s">
         <v>30</v>
       </c>
       <c r="B252" s="16">
@@ -12214,7 +12208,7 @@
       </c>
     </row>
     <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A253" s="41" t="s">
+      <c r="A253" t="s">
         <v>30</v>
       </c>
       <c r="B253" s="8">
@@ -12256,7 +12250,7 @@
       </c>
     </row>
     <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A254" s="41" t="s">
+      <c r="A254" t="s">
         <v>30</v>
       </c>
       <c r="B254" s="16">
@@ -12298,7 +12292,7 @@
       </c>
     </row>
     <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A255" s="41" t="s">
+      <c r="A255" t="s">
         <v>30</v>
       </c>
       <c r="B255" s="16">
@@ -12340,7 +12334,7 @@
       </c>
     </row>
     <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A256" s="41" t="s">
+      <c r="A256" t="s">
         <v>30</v>
       </c>
       <c r="B256" s="16">
@@ -12382,7 +12376,7 @@
       </c>
     </row>
     <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A257" s="41" t="s">
+      <c r="A257" t="s">
         <v>30</v>
       </c>
       <c r="B257" s="16">
@@ -12427,7 +12421,7 @@
       </c>
     </row>
     <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A258" s="41" t="s">
+      <c r="A258" t="s">
         <v>30</v>
       </c>
       <c r="B258" s="7">
@@ -12467,7 +12461,7 @@
       </c>
     </row>
     <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A259" s="41" t="s">
+      <c r="A259" t="s">
         <v>30</v>
       </c>
       <c r="B259" s="16">
@@ -12507,7 +12501,7 @@
       </c>
     </row>
     <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A260" s="41" t="s">
+      <c r="A260" t="s">
         <v>30</v>
       </c>
       <c r="B260" s="16">
@@ -12547,7 +12541,7 @@
       </c>
     </row>
     <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A261" s="41" t="s">
+      <c r="A261" t="s">
         <v>30</v>
       </c>
       <c r="B261" s="8">
@@ -12587,7 +12581,7 @@
       </c>
     </row>
     <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A262" s="41" t="s">
+      <c r="A262" t="s">
         <v>30</v>
       </c>
       <c r="B262" s="7">
@@ -12627,7 +12621,7 @@
       </c>
     </row>
     <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A263" s="41" t="s">
+      <c r="A263" t="s">
         <v>30</v>
       </c>
       <c r="B263" s="16">
@@ -12667,7 +12661,7 @@
       </c>
     </row>
     <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A264" s="41" t="s">
+      <c r="A264" t="s">
         <v>30</v>
       </c>
       <c r="B264" s="16">
@@ -12707,7 +12701,7 @@
       </c>
     </row>
     <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A265" s="41" t="s">
+      <c r="A265" t="s">
         <v>30</v>
       </c>
       <c r="B265" s="8">
@@ -12747,7 +12741,7 @@
       </c>
     </row>
     <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A266" s="41" t="s">
+      <c r="A266" t="s">
         <v>30</v>
       </c>
       <c r="B266" s="7">
@@ -12787,7 +12781,7 @@
       </c>
     </row>
     <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A267" s="41" t="s">
+      <c r="A267" t="s">
         <v>30</v>
       </c>
       <c r="B267" s="16">
@@ -12827,7 +12821,7 @@
       </c>
     </row>
     <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A268" s="41" t="s">
+      <c r="A268" t="s">
         <v>30</v>
       </c>
       <c r="B268" s="16">
@@ -12867,7 +12861,7 @@
       </c>
     </row>
     <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A269" s="41" t="s">
+      <c r="A269" t="s">
         <v>30</v>
       </c>
       <c r="B269" s="8">
@@ -12907,7 +12901,7 @@
       </c>
     </row>
     <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A270" s="41" t="s">
+      <c r="A270" t="s">
         <v>30</v>
       </c>
       <c r="B270" s="7">
@@ -12947,7 +12941,7 @@
       </c>
     </row>
     <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A271" s="41" t="s">
+      <c r="A271" t="s">
         <v>30</v>
       </c>
       <c r="B271" s="16">
@@ -12987,7 +12981,7 @@
       </c>
     </row>
     <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A272" s="41" t="s">
+      <c r="A272" t="s">
         <v>30</v>
       </c>
       <c r="B272" s="16">
@@ -13027,7 +13021,7 @@
       </c>
     </row>
     <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A273" s="41" t="s">
+      <c r="A273" t="s">
         <v>30</v>
       </c>
       <c r="B273" s="8">
@@ -13067,7 +13061,7 @@
       </c>
     </row>
     <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A274" s="41" t="s">
+      <c r="A274" t="s">
         <v>30</v>
       </c>
       <c r="B274" s="7">
@@ -13107,7 +13101,7 @@
       </c>
     </row>
     <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A275" s="41" t="s">
+      <c r="A275" t="s">
         <v>30</v>
       </c>
       <c r="B275" s="16">
@@ -13147,7 +13141,7 @@
       </c>
     </row>
     <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A276" s="41" t="s">
+      <c r="A276" t="s">
         <v>30</v>
       </c>
       <c r="B276" s="16">
@@ -13187,7 +13181,7 @@
       </c>
     </row>
     <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A277" s="41" t="s">
+      <c r="A277" t="s">
         <v>30</v>
       </c>
       <c r="B277" s="8">
@@ -13227,7 +13221,7 @@
       </c>
     </row>
     <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A278" s="41" t="s">
+      <c r="A278" t="s">
         <v>30</v>
       </c>
       <c r="B278" s="7">
@@ -13267,7 +13261,7 @@
       </c>
     </row>
     <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A279" s="41" t="s">
+      <c r="A279" t="s">
         <v>30</v>
       </c>
       <c r="B279" s="16">
@@ -13307,7 +13301,7 @@
       </c>
     </row>
     <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A280" s="41" t="s">
+      <c r="A280" t="s">
         <v>30</v>
       </c>
       <c r="B280" s="16">
@@ -13347,7 +13341,7 @@
       </c>
     </row>
     <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A281" s="41" t="s">
+      <c r="A281" t="s">
         <v>30</v>
       </c>
       <c r="B281" s="8">
@@ -13387,7 +13381,7 @@
       </c>
     </row>
     <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A282" s="41" t="s">
+      <c r="A282" t="s">
         <v>30</v>
       </c>
       <c r="B282" s="7">
@@ -13427,7 +13421,7 @@
       </c>
     </row>
     <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A283" s="41" t="s">
+      <c r="A283" t="s">
         <v>30</v>
       </c>
       <c r="B283" s="16">
@@ -13467,7 +13461,7 @@
       </c>
     </row>
     <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A284" s="41" t="s">
+      <c r="A284" t="s">
         <v>30</v>
       </c>
       <c r="B284" s="16">
@@ -13507,7 +13501,7 @@
       </c>
     </row>
     <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A285" s="41" t="s">
+      <c r="A285" t="s">
         <v>30</v>
       </c>
       <c r="B285" s="8">
@@ -13547,7 +13541,7 @@
       </c>
     </row>
     <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A286" s="41" t="s">
+      <c r="A286" t="s">
         <v>30</v>
       </c>
       <c r="B286" s="7">
@@ -13587,7 +13581,7 @@
       </c>
     </row>
     <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A287" s="41" t="s">
+      <c r="A287" t="s">
         <v>30</v>
       </c>
       <c r="B287" s="16">
@@ -13627,7 +13621,7 @@
       </c>
     </row>
     <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A288" s="41" t="s">
+      <c r="A288" t="s">
         <v>30</v>
       </c>
       <c r="B288" s="16">
@@ -13667,7 +13661,7 @@
       </c>
     </row>
     <row r="289" spans="1:18" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="41" t="s">
+      <c r="A289" t="s">
         <v>30</v>
       </c>
       <c r="B289" s="8">
@@ -13707,7 +13701,7 @@
       </c>
     </row>
     <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A290" s="41" t="s">
+      <c r="A290" t="s">
         <v>30</v>
       </c>
       <c r="B290" s="7">
@@ -13749,7 +13743,7 @@
       </c>
     </row>
     <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A291" s="41" t="s">
+      <c r="A291" t="s">
         <v>30</v>
       </c>
       <c r="B291" s="16">
@@ -13791,7 +13785,7 @@
       </c>
     </row>
     <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A292" s="41" t="s">
+      <c r="A292" t="s">
         <v>30</v>
       </c>
       <c r="B292" s="16">
@@ -13833,7 +13827,7 @@
       </c>
     </row>
     <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A293" s="41" t="s">
+      <c r="A293" t="s">
         <v>30</v>
       </c>
       <c r="B293" s="8">
@@ -13875,7 +13869,7 @@
       </c>
     </row>
     <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A294" s="41" t="s">
+      <c r="A294" t="s">
         <v>30</v>
       </c>
       <c r="B294" s="16">
@@ -13917,7 +13911,7 @@
       </c>
     </row>
     <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A295" s="41" t="s">
+      <c r="A295" t="s">
         <v>30</v>
       </c>
       <c r="B295" s="16">
@@ -13959,7 +13953,7 @@
       </c>
     </row>
     <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A296" s="41" t="s">
+      <c r="A296" t="s">
         <v>30</v>
       </c>
       <c r="B296" s="16">
@@ -14001,7 +13995,7 @@
       </c>
     </row>
     <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A297" s="41" t="s">
+      <c r="A297" t="s">
         <v>30</v>
       </c>
       <c r="B297" s="16">
@@ -14043,7 +14037,7 @@
       </c>
     </row>
     <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A298" s="41" t="s">
+      <c r="A298" t="s">
         <v>30</v>
       </c>
       <c r="B298" s="7">
@@ -14085,7 +14079,7 @@
       </c>
     </row>
     <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A299" s="41" t="s">
+      <c r="A299" t="s">
         <v>30</v>
       </c>
       <c r="B299" s="16">
@@ -14127,7 +14121,7 @@
       </c>
     </row>
     <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A300" s="41" t="s">
+      <c r="A300" t="s">
         <v>30</v>
       </c>
       <c r="B300" s="16">
@@ -14169,7 +14163,7 @@
       </c>
     </row>
     <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A301" s="41" t="s">
+      <c r="A301" t="s">
         <v>30</v>
       </c>
       <c r="B301" s="8">
@@ -14211,7 +14205,7 @@
       </c>
     </row>
     <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A302" s="41" t="s">
+      <c r="A302" t="s">
         <v>30</v>
       </c>
       <c r="B302" s="16">
@@ -14253,7 +14247,7 @@
       </c>
     </row>
     <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A303" s="41" t="s">
+      <c r="A303" t="s">
         <v>30</v>
       </c>
       <c r="B303" s="16">
@@ -14295,7 +14289,7 @@
       </c>
     </row>
     <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A304" s="41" t="s">
+      <c r="A304" t="s">
         <v>30</v>
       </c>
       <c r="B304" s="16">
@@ -14337,7 +14331,7 @@
       </c>
     </row>
     <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A305" s="41" t="s">
+      <c r="A305" t="s">
         <v>30</v>
       </c>
       <c r="B305" s="16">
@@ -14379,7 +14373,7 @@
       </c>
     </row>
     <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A306" s="41" t="s">
+      <c r="A306" t="s">
         <v>30</v>
       </c>
       <c r="B306" s="7">
@@ -14421,7 +14415,7 @@
       </c>
     </row>
     <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A307" s="41" t="s">
+      <c r="A307" t="s">
         <v>30</v>
       </c>
       <c r="B307" s="16">
@@ -14463,7 +14457,7 @@
       </c>
     </row>
     <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A308" s="41" t="s">
+      <c r="A308" t="s">
         <v>30</v>
       </c>
       <c r="B308" s="16">
@@ -14505,7 +14499,7 @@
       </c>
     </row>
     <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A309" s="41" t="s">
+      <c r="A309" t="s">
         <v>30</v>
       </c>
       <c r="B309" s="8">
@@ -14547,7 +14541,7 @@
       </c>
     </row>
     <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A310" s="41" t="s">
+      <c r="A310" t="s">
         <v>30</v>
       </c>
       <c r="B310" s="16">
@@ -14589,7 +14583,7 @@
       </c>
     </row>
     <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A311" s="41" t="s">
+      <c r="A311" t="s">
         <v>30</v>
       </c>
       <c r="B311" s="16">
@@ -14631,7 +14625,7 @@
       </c>
     </row>
     <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A312" s="41" t="s">
+      <c r="A312" t="s">
         <v>30</v>
       </c>
       <c r="B312" s="16">
@@ -14673,7 +14667,7 @@
       </c>
     </row>
     <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A313" s="41" t="s">
+      <c r="A313" t="s">
         <v>30</v>
       </c>
       <c r="B313" s="16">
@@ -14715,7 +14709,7 @@
       </c>
     </row>
     <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A314" s="41" t="s">
+      <c r="A314" t="s">
         <v>30</v>
       </c>
       <c r="B314" s="7">
@@ -14757,7 +14751,7 @@
       </c>
     </row>
     <row r="315" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A315" s="41" t="s">
+      <c r="A315" t="s">
         <v>30</v>
       </c>
       <c r="B315" s="16">
@@ -14799,7 +14793,7 @@
       </c>
     </row>
     <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A316" s="41" t="s">
+      <c r="A316" t="s">
         <v>30</v>
       </c>
       <c r="B316" s="16">
@@ -14841,7 +14835,7 @@
       </c>
     </row>
     <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A317" s="41" t="s">
+      <c r="A317" t="s">
         <v>30</v>
       </c>
       <c r="B317" s="8">
@@ -14883,7 +14877,7 @@
       </c>
     </row>
     <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A318" s="41" t="s">
+      <c r="A318" t="s">
         <v>30</v>
       </c>
       <c r="B318" s="16">
@@ -14925,7 +14919,7 @@
       </c>
     </row>
     <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A319" s="41" t="s">
+      <c r="A319" t="s">
         <v>30</v>
       </c>
       <c r="B319" s="16">
@@ -14967,7 +14961,7 @@
       </c>
     </row>
     <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A320" s="41" t="s">
+      <c r="A320" t="s">
         <v>30</v>
       </c>
       <c r="B320" s="16">
@@ -15009,7 +15003,7 @@
       </c>
     </row>
     <row r="321" spans="1:18" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A321" s="41" t="s">
+      <c r="A321" t="s">
         <v>30</v>
       </c>
       <c r="B321" s="29">
@@ -15051,7 +15045,7 @@
       </c>
     </row>
     <row r="322" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A322" s="41" t="s">
+      <c r="A322" t="s">
         <v>30</v>
       </c>
       <c r="B322" s="10">
@@ -15099,7 +15093,7 @@
       </c>
     </row>
     <row r="323" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A323" s="41" t="s">
+      <c r="A323" t="s">
         <v>30</v>
       </c>
       <c r="B323" s="5">
@@ -15147,7 +15141,7 @@
       </c>
     </row>
     <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A324" s="41" t="s">
+      <c r="A324" t="s">
         <v>30</v>
       </c>
       <c r="B324" s="5">
@@ -15195,7 +15189,7 @@
       </c>
     </row>
     <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A325" s="41" t="s">
+      <c r="A325" t="s">
         <v>30</v>
       </c>
       <c r="B325" s="5">
@@ -15243,7 +15237,7 @@
       </c>
     </row>
     <row r="326" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A326" s="41" t="s">
+      <c r="A326" t="s">
         <v>30</v>
       </c>
       <c r="B326" s="5">
@@ -15291,7 +15285,7 @@
       </c>
     </row>
     <row r="327" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A327" s="41" t="s">
+      <c r="A327" t="s">
         <v>30</v>
       </c>
       <c r="B327" s="5">
@@ -15339,7 +15333,7 @@
       </c>
     </row>
     <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A328" s="41" t="s">
+      <c r="A328" t="s">
         <v>30</v>
       </c>
       <c r="B328" s="5">
@@ -15387,7 +15381,7 @@
       </c>
     </row>
     <row r="329" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A329" s="41" t="s">
+      <c r="A329" t="s">
         <v>30</v>
       </c>
       <c r="B329" s="5">
@@ -15435,7 +15429,7 @@
       </c>
     </row>
     <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A330" s="41" t="s">
+      <c r="A330" t="s">
         <v>30</v>
       </c>
       <c r="B330" s="5">
@@ -15483,7 +15477,7 @@
       </c>
     </row>
     <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A331" s="41" t="s">
+      <c r="A331" t="s">
         <v>30</v>
       </c>
       <c r="B331" s="5">
@@ -15531,7 +15525,7 @@
       </c>
     </row>
     <row r="332" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A332" s="41" t="s">
+      <c r="A332" t="s">
         <v>30</v>
       </c>
       <c r="B332" s="5">
@@ -15579,7 +15573,7 @@
       </c>
     </row>
     <row r="333" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A333" s="41" t="s">
+      <c r="A333" t="s">
         <v>30</v>
       </c>
       <c r="B333" s="5">
@@ -15627,7 +15621,7 @@
       </c>
     </row>
     <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A334" s="41" t="s">
+      <c r="A334" t="s">
         <v>30</v>
       </c>
       <c r="B334" s="5">
@@ -15675,7 +15669,7 @@
       </c>
     </row>
     <row r="335" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A335" s="41" t="s">
+      <c r="A335" t="s">
         <v>30</v>
       </c>
       <c r="B335" s="5">
@@ -15723,7 +15717,7 @@
       </c>
     </row>
     <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A336" s="41" t="s">
+      <c r="A336" t="s">
         <v>30</v>
       </c>
       <c r="B336" s="5">
@@ -15771,7 +15765,7 @@
       </c>
     </row>
     <row r="337" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A337" s="41" t="s">
+      <c r="A337" t="s">
         <v>30</v>
       </c>
       <c r="B337" s="5">
@@ -15819,7 +15813,7 @@
       </c>
     </row>
     <row r="338" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A338" s="41" t="s">
+      <c r="A338" t="s">
         <v>30</v>
       </c>
       <c r="B338" s="5">
@@ -15867,7 +15861,7 @@
       </c>
     </row>
     <row r="339" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A339" s="41" t="s">
+      <c r="A339" t="s">
         <v>30</v>
       </c>
       <c r="B339" s="5">
@@ -15915,7 +15909,7 @@
       </c>
     </row>
     <row r="340" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A340" s="41" t="s">
+      <c r="A340" t="s">
         <v>30</v>
       </c>
       <c r="B340" s="5">
@@ -15963,7 +15957,7 @@
       </c>
     </row>
     <row r="341" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A341" s="41" t="s">
+      <c r="A341" t="s">
         <v>30</v>
       </c>
       <c r="B341" s="5">
@@ -16011,7 +16005,7 @@
       </c>
     </row>
     <row r="342" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A342" s="41" t="s">
+      <c r="A342" t="s">
         <v>30</v>
       </c>
       <c r="B342" s="5">
@@ -16059,7 +16053,7 @@
       </c>
     </row>
     <row r="343" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A343" s="41" t="s">
+      <c r="A343" t="s">
         <v>30</v>
       </c>
       <c r="B343" s="5">
@@ -16107,7 +16101,7 @@
       </c>
     </row>
     <row r="344" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A344" s="41" t="s">
+      <c r="A344" t="s">
         <v>30</v>
       </c>
       <c r="B344" s="5">
@@ -16155,7 +16149,7 @@
       </c>
     </row>
     <row r="345" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A345" s="41" t="s">
+      <c r="A345" t="s">
         <v>30</v>
       </c>
       <c r="B345" s="5">
@@ -16203,7 +16197,7 @@
       </c>
     </row>
     <row r="346" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A346" s="41" t="s">
+      <c r="A346" t="s">
         <v>30</v>
       </c>
       <c r="B346" s="5">
@@ -16251,7 +16245,7 @@
       </c>
     </row>
     <row r="347" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A347" s="41" t="s">
+      <c r="A347" t="s">
         <v>30</v>
       </c>
       <c r="B347" s="5">
@@ -16299,7 +16293,7 @@
       </c>
     </row>
     <row r="348" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A348" s="41" t="s">
+      <c r="A348" t="s">
         <v>30</v>
       </c>
       <c r="B348" s="5">
@@ -16347,7 +16341,7 @@
       </c>
     </row>
     <row r="349" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A349" s="41" t="s">
+      <c r="A349" t="s">
         <v>30</v>
       </c>
       <c r="B349" s="5">
@@ -16395,7 +16389,7 @@
       </c>
     </row>
     <row r="350" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A350" s="41" t="s">
+      <c r="A350" t="s">
         <v>30</v>
       </c>
       <c r="B350" s="5">
@@ -16443,7 +16437,7 @@
       </c>
     </row>
     <row r="351" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A351" s="41" t="s">
+      <c r="A351" t="s">
         <v>30</v>
       </c>
       <c r="B351" s="5">
@@ -16491,7 +16485,7 @@
       </c>
     </row>
     <row r="352" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A352" s="41" t="s">
+      <c r="A352" t="s">
         <v>30</v>
       </c>
       <c r="B352" s="5">
@@ -16539,7 +16533,7 @@
       </c>
     </row>
     <row r="353" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A353" s="41" t="s">
+      <c r="A353" t="s">
         <v>30</v>
       </c>
       <c r="B353" s="5">
@@ -16587,7 +16581,7 @@
       </c>
     </row>
     <row r="354" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A354" s="41" t="s">
+      <c r="A354" t="s">
         <v>30</v>
       </c>
       <c r="B354" s="5">
@@ -16635,7 +16629,7 @@
       </c>
     </row>
     <row r="355" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A355" s="41" t="s">
+      <c r="A355" t="s">
         <v>30</v>
       </c>
       <c r="B355" s="5">
@@ -16683,7 +16677,7 @@
       </c>
     </row>
     <row r="356" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A356" s="41" t="s">
+      <c r="A356" t="s">
         <v>30</v>
       </c>
       <c r="B356" s="5">
@@ -16731,7 +16725,7 @@
       </c>
     </row>
     <row r="357" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A357" s="41" t="s">
+      <c r="A357" t="s">
         <v>30</v>
       </c>
       <c r="B357" s="5">
@@ -16779,7 +16773,7 @@
       </c>
     </row>
     <row r="358" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A358" s="41" t="s">
+      <c r="A358" t="s">
         <v>30</v>
       </c>
       <c r="B358" s="5">
@@ -16827,7 +16821,7 @@
       </c>
     </row>
     <row r="359" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A359" s="41" t="s">
+      <c r="A359" t="s">
         <v>30</v>
       </c>
       <c r="B359" s="5">
@@ -16875,7 +16869,7 @@
       </c>
     </row>
     <row r="360" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A360" s="41" t="s">
+      <c r="A360" t="s">
         <v>30</v>
       </c>
       <c r="B360" s="5">
@@ -16923,7 +16917,7 @@
       </c>
     </row>
     <row r="361" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A361" s="41" t="s">
+      <c r="A361" t="s">
         <v>30</v>
       </c>
       <c r="B361" s="5">
@@ -16971,7 +16965,7 @@
       </c>
     </row>
     <row r="362" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A362" s="41" t="s">
+      <c r="A362" t="s">
         <v>30</v>
       </c>
       <c r="B362" s="5">
@@ -17019,7 +17013,7 @@
       </c>
     </row>
     <row r="363" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A363" s="41" t="s">
+      <c r="A363" t="s">
         <v>30</v>
       </c>
       <c r="B363" s="5">
@@ -17067,7 +17061,7 @@
       </c>
     </row>
     <row r="364" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A364" s="41" t="s">
+      <c r="A364" t="s">
         <v>30</v>
       </c>
       <c r="B364" s="5">
@@ -17115,7 +17109,7 @@
       </c>
     </row>
     <row r="365" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A365" s="41" t="s">
+      <c r="A365" t="s">
         <v>30</v>
       </c>
       <c r="B365" s="5">
@@ -17163,7 +17157,7 @@
       </c>
     </row>
     <row r="366" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A366" s="41" t="s">
+      <c r="A366" t="s">
         <v>30</v>
       </c>
       <c r="B366" s="5">
@@ -17211,7 +17205,7 @@
       </c>
     </row>
     <row r="367" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A367" s="41" t="s">
+      <c r="A367" t="s">
         <v>30</v>
       </c>
       <c r="B367" s="5">
@@ -17259,7 +17253,7 @@
       </c>
     </row>
     <row r="368" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A368" s="41" t="s">
+      <c r="A368" t="s">
         <v>30</v>
       </c>
       <c r="B368" s="5">
@@ -17307,7 +17301,7 @@
       </c>
     </row>
     <row r="369" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A369" s="41" t="s">
+      <c r="A369" t="s">
         <v>30</v>
       </c>
       <c r="B369" s="5">
@@ -17355,7 +17349,7 @@
       </c>
     </row>
     <row r="370" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A370" s="41" t="s">
+      <c r="A370" t="s">
         <v>30</v>
       </c>
       <c r="B370" s="15">
@@ -17403,7 +17397,7 @@
       </c>
     </row>
     <row r="371" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A371" s="41" t="s">
+      <c r="A371" t="s">
         <v>30</v>
       </c>
       <c r="B371" s="15">
@@ -17451,7 +17445,7 @@
       </c>
     </row>
     <row r="372" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A372" s="41" t="s">
+      <c r="A372" t="s">
         <v>30</v>
       </c>
       <c r="B372" s="15">
@@ -17499,7 +17493,7 @@
       </c>
     </row>
     <row r="373" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A373" s="41" t="s">
+      <c r="A373" t="s">
         <v>30</v>
       </c>
       <c r="B373" s="15">
@@ -17547,7 +17541,7 @@
       </c>
     </row>
     <row r="374" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A374" s="41" t="s">
+      <c r="A374" t="s">
         <v>30</v>
       </c>
       <c r="B374" s="5">
@@ -17595,7 +17589,7 @@
       </c>
     </row>
     <row r="375" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A375" s="41" t="s">
+      <c r="A375" t="s">
         <v>30</v>
       </c>
       <c r="B375" s="5">
@@ -17643,7 +17637,7 @@
       </c>
     </row>
     <row r="376" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A376" s="41" t="s">
+      <c r="A376" t="s">
         <v>30</v>
       </c>
       <c r="B376" s="5">
@@ -17691,7 +17685,7 @@
       </c>
     </row>
     <row r="377" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A377" s="41" t="s">
+      <c r="A377" t="s">
         <v>30</v>
       </c>
       <c r="B377" s="5">
@@ -17739,7 +17733,7 @@
       </c>
     </row>
     <row r="378" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A378" s="41" t="s">
+      <c r="A378" t="s">
         <v>30</v>
       </c>
       <c r="B378" s="5">
@@ -17787,7 +17781,7 @@
       </c>
     </row>
     <row r="379" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A379" s="41" t="s">
+      <c r="A379" t="s">
         <v>30</v>
       </c>
       <c r="B379" s="5">
@@ -17835,7 +17829,7 @@
       </c>
     </row>
     <row r="380" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A380" s="41" t="s">
+      <c r="A380" t="s">
         <v>30</v>
       </c>
       <c r="B380" s="5">
@@ -17883,7 +17877,7 @@
       </c>
     </row>
     <row r="381" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A381" s="41" t="s">
+      <c r="A381" t="s">
         <v>30</v>
       </c>
       <c r="B381" s="5">
@@ -17931,7 +17925,7 @@
       </c>
     </row>
     <row r="382" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A382" s="41" t="s">
+      <c r="A382" t="s">
         <v>30</v>
       </c>
       <c r="B382" s="5">
@@ -17979,7 +17973,7 @@
       </c>
     </row>
     <row r="383" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A383" s="41" t="s">
+      <c r="A383" t="s">
         <v>30</v>
       </c>
       <c r="B383" s="5">
@@ -18027,7 +18021,7 @@
       </c>
     </row>
     <row r="384" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A384" s="41" t="s">
+      <c r="A384" t="s">
         <v>30</v>
       </c>
       <c r="B384" s="5">
@@ -18075,7 +18069,7 @@
       </c>
     </row>
     <row r="385" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A385" s="41" t="s">
+      <c r="A385" t="s">
         <v>30</v>
       </c>
       <c r="B385" s="5">
@@ -18123,7 +18117,7 @@
       </c>
     </row>
     <row r="386" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A386" s="41" t="s">
+      <c r="A386" t="s">
         <v>30</v>
       </c>
       <c r="B386" s="5">
@@ -18171,7 +18165,7 @@
       </c>
     </row>
     <row r="387" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A387" s="41" t="s">
+      <c r="A387" t="s">
         <v>30</v>
       </c>
       <c r="B387" s="5">
@@ -18219,7 +18213,7 @@
       </c>
     </row>
     <row r="388" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A388" s="41" t="s">
+      <c r="A388" t="s">
         <v>30</v>
       </c>
       <c r="B388" s="5">
@@ -18267,7 +18261,7 @@
       </c>
     </row>
     <row r="389" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A389" s="41" t="s">
+      <c r="A389" t="s">
         <v>30</v>
       </c>
       <c r="B389" s="5">
@@ -18315,7 +18309,7 @@
       </c>
     </row>
     <row r="390" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A390" s="41" t="s">
+      <c r="A390" t="s">
         <v>30</v>
       </c>
       <c r="B390" s="5">
@@ -18363,7 +18357,7 @@
       </c>
     </row>
     <row r="391" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A391" s="41" t="s">
+      <c r="A391" t="s">
         <v>30</v>
       </c>
       <c r="B391" s="5">
@@ -18411,7 +18405,7 @@
       </c>
     </row>
     <row r="392" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A392" s="41" t="s">
+      <c r="A392" t="s">
         <v>30</v>
       </c>
       <c r="B392" s="5">
@@ -18459,7 +18453,7 @@
       </c>
     </row>
     <row r="393" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A393" s="41" t="s">
+      <c r="A393" t="s">
         <v>30</v>
       </c>
       <c r="B393" s="5">
@@ -18507,7 +18501,7 @@
       </c>
     </row>
     <row r="394" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A394" s="41" t="s">
+      <c r="A394" t="s">
         <v>30</v>
       </c>
       <c r="B394" s="5">
@@ -18555,7 +18549,7 @@
       </c>
     </row>
     <row r="395" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A395" s="41" t="s">
+      <c r="A395" t="s">
         <v>30</v>
       </c>
       <c r="B395" s="5">
@@ -18603,7 +18597,7 @@
       </c>
     </row>
     <row r="396" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A396" s="41" t="s">
+      <c r="A396" t="s">
         <v>30</v>
       </c>
       <c r="B396" s="5">
@@ -18651,7 +18645,7 @@
       </c>
     </row>
     <row r="397" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A397" s="41" t="s">
+      <c r="A397" t="s">
         <v>30</v>
       </c>
       <c r="B397" s="5">
@@ -18699,7 +18693,7 @@
       </c>
     </row>
     <row r="398" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A398" s="41" t="s">
+      <c r="A398" t="s">
         <v>30</v>
       </c>
       <c r="B398" s="5">
@@ -18747,7 +18741,7 @@
       </c>
     </row>
     <row r="399" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A399" s="41" t="s">
+      <c r="A399" t="s">
         <v>30</v>
       </c>
       <c r="B399" s="5">
@@ -18795,7 +18789,7 @@
       </c>
     </row>
     <row r="400" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A400" s="41" t="s">
+      <c r="A400" t="s">
         <v>30</v>
       </c>
       <c r="B400" s="5">
@@ -18843,7 +18837,7 @@
       </c>
     </row>
     <row r="401" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A401" s="41" t="s">
+      <c r="A401" t="s">
         <v>30</v>
       </c>
       <c r="B401" s="5">
@@ -18891,7 +18885,7 @@
       </c>
     </row>
     <row r="402" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A402" s="41" t="s">
+      <c r="A402" t="s">
         <v>30</v>
       </c>
       <c r="B402" s="5">
@@ -18939,7 +18933,7 @@
       </c>
     </row>
     <row r="403" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A403" s="41" t="s">
+      <c r="A403" t="s">
         <v>30</v>
       </c>
       <c r="B403" s="5">
@@ -18987,7 +18981,7 @@
       </c>
     </row>
     <row r="404" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A404" s="41" t="s">
+      <c r="A404" t="s">
         <v>30</v>
       </c>
       <c r="B404" s="5">
@@ -19035,7 +19029,7 @@
       </c>
     </row>
     <row r="405" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A405" s="41" t="s">
+      <c r="A405" t="s">
         <v>30</v>
       </c>
       <c r="B405" s="5">
@@ -19083,7 +19077,7 @@
       </c>
     </row>
     <row r="406" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A406" s="41" t="s">
+      <c r="A406" t="s">
         <v>30</v>
       </c>
       <c r="B406" s="5">
@@ -19131,7 +19125,7 @@
       </c>
     </row>
     <row r="407" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A407" s="41" t="s">
+      <c r="A407" t="s">
         <v>30</v>
       </c>
       <c r="B407" s="5">
@@ -19179,7 +19173,7 @@
       </c>
     </row>
     <row r="408" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A408" s="41" t="s">
+      <c r="A408" t="s">
         <v>30</v>
       </c>
       <c r="B408" s="5">
@@ -19227,7 +19221,7 @@
       </c>
     </row>
     <row r="409" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A409" s="41" t="s">
+      <c r="A409" t="s">
         <v>30</v>
       </c>
       <c r="B409" s="5">
@@ -19275,7 +19269,7 @@
       </c>
     </row>
     <row r="410" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A410" s="41" t="s">
+      <c r="A410" t="s">
         <v>30</v>
       </c>
       <c r="B410" s="5">
@@ -19322,8 +19316,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="411" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A411" s="41" t="s">
+    <row r="411" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="A411" t="s">
         <v>30</v>
       </c>
       <c r="B411" s="5">
@@ -19367,11 +19361,11 @@
         <v>214.75153764581125</v>
       </c>
       <c r="R411" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A412" s="41" t="s">
+      <c r="A412" t="s">
         <v>30</v>
       </c>
       <c r="B412" s="5">
@@ -19419,7 +19413,7 @@
       </c>
     </row>
     <row r="413" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A413" s="41" t="s">
+      <c r="A413" t="s">
         <v>30</v>
       </c>
       <c r="B413" s="5">
@@ -19467,7 +19461,7 @@
       </c>
     </row>
     <row r="414" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A414" s="41" t="s">
+      <c r="A414" t="s">
         <v>30</v>
       </c>
       <c r="B414" s="5">
@@ -19515,7 +19509,7 @@
       </c>
     </row>
     <row r="415" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A415" s="41" t="s">
+      <c r="A415" t="s">
         <v>30</v>
       </c>
       <c r="B415" s="5">
@@ -19563,7 +19557,7 @@
       </c>
     </row>
     <row r="416" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A416" s="41" t="s">
+      <c r="A416" t="s">
         <v>30</v>
       </c>
       <c r="B416" s="5">
@@ -19611,7 +19605,7 @@
       </c>
     </row>
     <row r="417" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A417" s="41" t="s">
+      <c r="A417" t="s">
         <v>30</v>
       </c>
       <c r="B417" s="5">
@@ -19659,7 +19653,7 @@
       </c>
     </row>
     <row r="418" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A418" s="41" t="s">
+      <c r="A418" t="s">
         <v>30</v>
       </c>
       <c r="B418" s="5">
@@ -19707,7 +19701,7 @@
       </c>
     </row>
     <row r="419" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A419" s="41" t="s">
+      <c r="A419" t="s">
         <v>30</v>
       </c>
       <c r="B419" s="5">
@@ -19755,7 +19749,7 @@
       </c>
     </row>
     <row r="420" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A420" s="41" t="s">
+      <c r="A420" t="s">
         <v>30</v>
       </c>
       <c r="B420" s="5">
@@ -19803,7 +19797,7 @@
       </c>
     </row>
     <row r="421" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A421" s="41" t="s">
+      <c r="A421" t="s">
         <v>30</v>
       </c>
       <c r="B421" s="5">
@@ -19851,7 +19845,7 @@
       </c>
     </row>
     <row r="422" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A422" s="41" t="s">
+      <c r="A422" t="s">
         <v>30</v>
       </c>
       <c r="B422" s="5">
@@ -19899,7 +19893,7 @@
       </c>
     </row>
     <row r="423" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A423" s="41" t="s">
+      <c r="A423" t="s">
         <v>30</v>
       </c>
       <c r="B423" s="5">
@@ -19947,7 +19941,7 @@
       </c>
     </row>
     <row r="424" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A424" s="41" t="s">
+      <c r="A424" t="s">
         <v>30</v>
       </c>
       <c r="B424" s="5">
@@ -19995,7 +19989,7 @@
       </c>
     </row>
     <row r="425" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A425" s="41" t="s">
+      <c r="A425" t="s">
         <v>30</v>
       </c>
       <c r="B425" s="5">
@@ -20043,7 +20037,7 @@
       </c>
     </row>
     <row r="426" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A426" s="41" t="s">
+      <c r="A426" t="s">
         <v>30</v>
       </c>
       <c r="B426" s="5">
@@ -20091,7 +20085,7 @@
       </c>
     </row>
     <row r="427" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A427" s="41" t="s">
+      <c r="A427" t="s">
         <v>30</v>
       </c>
       <c r="B427" s="5">
@@ -20139,7 +20133,7 @@
       </c>
     </row>
     <row r="428" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A428" s="41" t="s">
+      <c r="A428" t="s">
         <v>30</v>
       </c>
       <c r="B428" s="5">
@@ -20187,7 +20181,7 @@
       </c>
     </row>
     <row r="429" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A429" s="41" t="s">
+      <c r="A429" t="s">
         <v>30</v>
       </c>
       <c r="B429" s="5">
@@ -20235,7 +20229,7 @@
       </c>
     </row>
     <row r="430" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A430" s="41" t="s">
+      <c r="A430" t="s">
         <v>30</v>
       </c>
       <c r="B430" s="5">
@@ -20283,7 +20277,7 @@
       </c>
     </row>
     <row r="431" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A431" s="41" t="s">
+      <c r="A431" t="s">
         <v>30</v>
       </c>
       <c r="B431" s="5">
@@ -20331,7 +20325,7 @@
       </c>
     </row>
     <row r="432" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A432" s="41" t="s">
+      <c r="A432" t="s">
         <v>30</v>
       </c>
       <c r="B432" s="5">
@@ -20379,7 +20373,7 @@
       </c>
     </row>
     <row r="433" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A433" s="41" t="s">
+      <c r="A433" t="s">
         <v>30</v>
       </c>
       <c r="B433" s="5">
@@ -20427,7 +20421,7 @@
       </c>
     </row>
     <row r="434" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A434" s="41" t="s">
+      <c r="A434" t="s">
         <v>30</v>
       </c>
       <c r="B434" s="15">
@@ -20475,7 +20469,7 @@
       </c>
     </row>
     <row r="435" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A435" s="41" t="s">
+      <c r="A435" t="s">
         <v>30</v>
       </c>
       <c r="B435" s="15">
@@ -20523,7 +20517,7 @@
       </c>
     </row>
     <row r="436" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A436" s="41" t="s">
+      <c r="A436" t="s">
         <v>30</v>
       </c>
       <c r="B436" s="15">
@@ -20571,7 +20565,7 @@
       </c>
     </row>
     <row r="437" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A437" s="41" t="s">
+      <c r="A437" t="s">
         <v>30</v>
       </c>
       <c r="B437" s="15">
@@ -20619,7 +20613,7 @@
       </c>
     </row>
     <row r="438" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A438" s="41" t="s">
+      <c r="A438" t="s">
         <v>30</v>
       </c>
       <c r="B438" s="5">
@@ -20667,7 +20661,7 @@
       </c>
     </row>
     <row r="439" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A439" s="41" t="s">
+      <c r="A439" t="s">
         <v>30</v>
       </c>
       <c r="B439" s="5">
@@ -20715,7 +20709,7 @@
       </c>
     </row>
     <row r="440" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A440" s="41" t="s">
+      <c r="A440" t="s">
         <v>30</v>
       </c>
       <c r="B440" s="5">
@@ -20763,7 +20757,7 @@
       </c>
     </row>
     <row r="441" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A441" s="41" t="s">
+      <c r="A441" t="s">
         <v>30</v>
       </c>
       <c r="B441" s="5">
@@ -20811,7 +20805,7 @@
       </c>
     </row>
     <row r="442" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A442" s="41" t="s">
+      <c r="A442" t="s">
         <v>30</v>
       </c>
       <c r="B442" s="5">
@@ -20859,7 +20853,7 @@
       </c>
     </row>
     <row r="443" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A443" s="41" t="s">
+      <c r="A443" t="s">
         <v>30</v>
       </c>
       <c r="B443" s="5">
@@ -20907,7 +20901,7 @@
       </c>
     </row>
     <row r="444" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A444" s="41" t="s">
+      <c r="A444" t="s">
         <v>30</v>
       </c>
       <c r="B444" s="5">
@@ -20955,7 +20949,7 @@
       </c>
     </row>
     <row r="445" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A445" s="41" t="s">
+      <c r="A445" t="s">
         <v>30</v>
       </c>
       <c r="B445" s="5">
@@ -21003,7 +20997,7 @@
       </c>
     </row>
     <row r="446" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A446" s="41" t="s">
+      <c r="A446" t="s">
         <v>30</v>
       </c>
       <c r="B446" s="5">
@@ -21051,7 +21045,7 @@
       </c>
     </row>
     <row r="447" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A447" s="41" t="s">
+      <c r="A447" t="s">
         <v>30</v>
       </c>
       <c r="B447" s="5">
@@ -21099,7 +21093,7 @@
       </c>
     </row>
     <row r="448" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A448" s="41" t="s">
+      <c r="A448" t="s">
         <v>30</v>
       </c>
       <c r="B448" s="5">
@@ -21147,7 +21141,7 @@
       </c>
     </row>
     <row r="449" spans="1:18" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A449" s="41" t="s">
+      <c r="A449" t="s">
         <v>30</v>
       </c>
       <c r="B449" s="30">
@@ -21195,7 +21189,7 @@
       </c>
     </row>
     <row r="450" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A450" s="45" t="s">
+      <c r="A450" t="s">
         <v>31</v>
       </c>
       <c r="B450" s="15">
@@ -21204,34 +21198,34 @@
       <c r="C450">
         <v>0</v>
       </c>
-      <c r="D450" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E450" s="45">
-        <v>1</v>
-      </c>
-      <c r="F450" s="45">
-        <v>1</v>
-      </c>
-      <c r="G450" s="45" t="s">
+      <c r="D450" t="s">
+        <v>5</v>
+      </c>
+      <c r="E450">
+        <v>1</v>
+      </c>
+      <c r="F450">
+        <v>1</v>
+      </c>
+      <c r="G450" t="s">
         <v>12</v>
       </c>
-      <c r="H450" s="45">
+      <c r="H450">
         <v>131</v>
       </c>
-      <c r="I450" s="45">
-        <v>1</v>
-      </c>
-      <c r="J450" s="45" t="s">
+      <c r="I450">
+        <v>1</v>
+      </c>
+      <c r="J450" t="s">
         <v>36</v>
       </c>
-      <c r="K450" s="45">
-        <v>1</v>
-      </c>
-      <c r="L450" s="45" t="s">
+      <c r="K450">
+        <v>1</v>
+      </c>
+      <c r="L450" t="s">
         <v>7</v>
       </c>
-      <c r="M450" s="46">
+      <c r="M450" s="42">
         <v>412.8</v>
       </c>
       <c r="R450" t="s">
@@ -21239,7 +21233,7 @@
       </c>
     </row>
     <row r="451" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A451" s="45" t="s">
+      <c r="A451" t="s">
         <v>31</v>
       </c>
       <c r="B451" s="15">
@@ -21248,34 +21242,34 @@
       <c r="C451">
         <v>0</v>
       </c>
-      <c r="D451" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E451" s="45">
-        <v>1</v>
-      </c>
-      <c r="F451" s="45">
-        <v>1</v>
-      </c>
-      <c r="G451" s="45" t="s">
+      <c r="D451" t="s">
+        <v>5</v>
+      </c>
+      <c r="E451">
+        <v>1</v>
+      </c>
+      <c r="F451">
+        <v>1</v>
+      </c>
+      <c r="G451" t="s">
         <v>12</v>
       </c>
-      <c r="H451" s="45">
+      <c r="H451">
         <v>132</v>
       </c>
-      <c r="I451" s="45">
-        <v>2</v>
-      </c>
-      <c r="J451" s="45" t="s">
+      <c r="I451">
+        <v>2</v>
+      </c>
+      <c r="J451" t="s">
         <v>36</v>
       </c>
-      <c r="K451" s="45">
-        <v>1</v>
-      </c>
-      <c r="L451" s="45" t="s">
+      <c r="K451">
+        <v>1</v>
+      </c>
+      <c r="L451" t="s">
         <v>7</v>
       </c>
-      <c r="M451" s="46">
+      <c r="M451" s="42">
         <v>736.7</v>
       </c>
       <c r="R451" t="s">
@@ -21283,7 +21277,7 @@
       </c>
     </row>
     <row r="452" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A452" s="45" t="s">
+      <c r="A452" t="s">
         <v>31</v>
       </c>
       <c r="B452" s="15">
@@ -21292,34 +21286,34 @@
       <c r="C452">
         <v>0</v>
       </c>
-      <c r="D452" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E452" s="45">
-        <v>1</v>
-      </c>
-      <c r="F452" s="45">
-        <v>1</v>
-      </c>
-      <c r="G452" s="45" t="s">
+      <c r="D452" t="s">
+        <v>5</v>
+      </c>
+      <c r="E452">
+        <v>1</v>
+      </c>
+      <c r="F452">
+        <v>1</v>
+      </c>
+      <c r="G452" t="s">
         <v>12</v>
       </c>
-      <c r="H452" s="45">
+      <c r="H452">
         <v>133</v>
       </c>
-      <c r="I452" s="45">
+      <c r="I452">
         <v>3</v>
       </c>
-      <c r="J452" s="45" t="s">
+      <c r="J452" t="s">
         <v>36</v>
       </c>
-      <c r="K452" s="45">
-        <v>1</v>
-      </c>
-      <c r="L452" s="45" t="s">
+      <c r="K452">
+        <v>1</v>
+      </c>
+      <c r="L452" t="s">
         <v>7</v>
       </c>
-      <c r="M452" s="46">
+      <c r="M452" s="42">
         <v>408</v>
       </c>
       <c r="R452" t="s">
@@ -21327,40 +21321,40 @@
       </c>
     </row>
     <row r="453" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A453" s="45" t="s">
+      <c r="A453" t="s">
         <v>31</v>
       </c>
       <c r="B453" s="15">
         <v>45914.673611111109</v>
       </c>
-      <c r="D453" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E453" s="45">
-        <v>1</v>
-      </c>
-      <c r="F453" s="45">
-        <v>1</v>
-      </c>
-      <c r="G453" s="45" t="s">
+      <c r="D453" t="s">
+        <v>5</v>
+      </c>
+      <c r="E453">
+        <v>1</v>
+      </c>
+      <c r="F453">
+        <v>1</v>
+      </c>
+      <c r="G453" t="s">
         <v>12</v>
       </c>
-      <c r="H453" s="45">
+      <c r="H453">
         <v>131</v>
       </c>
-      <c r="I453" s="45">
-        <v>1</v>
-      </c>
-      <c r="J453" s="45" t="s">
+      <c r="I453">
+        <v>1</v>
+      </c>
+      <c r="J453" t="s">
         <v>36</v>
       </c>
-      <c r="K453" s="45">
-        <v>2</v>
-      </c>
-      <c r="L453" s="45" t="s">
+      <c r="K453">
+        <v>2</v>
+      </c>
+      <c r="L453" t="s">
         <v>7</v>
       </c>
-      <c r="M453" s="46">
+      <c r="M453" s="42">
         <v>424</v>
       </c>
       <c r="R453" t="s">
@@ -21368,40 +21362,40 @@
       </c>
     </row>
     <row r="454" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A454" s="45" t="s">
+      <c r="A454" t="s">
         <v>31</v>
       </c>
       <c r="B454" s="15">
         <v>45914.673611111109</v>
       </c>
-      <c r="D454" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E454" s="45">
-        <v>1</v>
-      </c>
-      <c r="F454" s="45">
-        <v>1</v>
-      </c>
-      <c r="G454" s="45" t="s">
+      <c r="D454" t="s">
+        <v>5</v>
+      </c>
+      <c r="E454">
+        <v>1</v>
+      </c>
+      <c r="F454">
+        <v>1</v>
+      </c>
+      <c r="G454" t="s">
         <v>12</v>
       </c>
-      <c r="H454" s="45">
+      <c r="H454">
         <v>132</v>
       </c>
-      <c r="I454" s="45">
-        <v>2</v>
-      </c>
-      <c r="J454" s="45" t="s">
+      <c r="I454">
+        <v>2</v>
+      </c>
+      <c r="J454" t="s">
         <v>36</v>
       </c>
-      <c r="K454" s="45">
-        <v>2</v>
-      </c>
-      <c r="L454" s="45" t="s">
+      <c r="K454">
+        <v>2</v>
+      </c>
+      <c r="L454" t="s">
         <v>7</v>
       </c>
-      <c r="M454" s="46">
+      <c r="M454" s="42">
         <v>756.5</v>
       </c>
       <c r="R454" t="s">
@@ -21409,40 +21403,40 @@
       </c>
     </row>
     <row r="455" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A455" s="45" t="s">
+      <c r="A455" t="s">
         <v>31</v>
       </c>
       <c r="B455" s="15">
         <v>45914.673611111109</v>
       </c>
-      <c r="D455" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E455" s="45">
-        <v>1</v>
-      </c>
-      <c r="F455" s="45">
-        <v>1</v>
-      </c>
-      <c r="G455" s="45" t="s">
+      <c r="D455" t="s">
+        <v>5</v>
+      </c>
+      <c r="E455">
+        <v>1</v>
+      </c>
+      <c r="F455">
+        <v>1</v>
+      </c>
+      <c r="G455" t="s">
         <v>12</v>
       </c>
-      <c r="H455" s="45">
+      <c r="H455">
         <v>133</v>
       </c>
-      <c r="I455" s="45">
+      <c r="I455">
         <v>3</v>
       </c>
-      <c r="J455" s="45" t="s">
+      <c r="J455" t="s">
         <v>36</v>
       </c>
-      <c r="K455" s="45">
-        <v>2</v>
-      </c>
-      <c r="L455" s="45" t="s">
+      <c r="K455">
+        <v>2</v>
+      </c>
+      <c r="L455" t="s">
         <v>7</v>
       </c>
-      <c r="M455" s="46">
+      <c r="M455" s="42">
         <v>396.4</v>
       </c>
       <c r="R455" t="s">
@@ -21450,46 +21444,46 @@
       </c>
     </row>
     <row r="456" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A456" s="45" t="s">
+      <c r="A456" t="s">
         <v>31</v>
       </c>
       <c r="B456" s="15">
         <v>45914.674305555556</v>
       </c>
-      <c r="D456" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E456" s="45">
-        <v>1</v>
-      </c>
-      <c r="F456" s="45">
-        <v>1</v>
-      </c>
-      <c r="G456" s="45" t="s">
+      <c r="D456" t="s">
+        <v>5</v>
+      </c>
+      <c r="E456">
+        <v>1</v>
+      </c>
+      <c r="F456">
+        <v>1</v>
+      </c>
+      <c r="G456" t="s">
         <v>12</v>
       </c>
-      <c r="H456" s="45">
+      <c r="H456">
         <v>131</v>
       </c>
-      <c r="I456" s="45">
-        <v>1</v>
-      </c>
-      <c r="J456" s="45" t="s">
+      <c r="I456">
+        <v>1</v>
+      </c>
+      <c r="J456" t="s">
         <v>36</v>
       </c>
-      <c r="K456" s="45">
-        <v>2</v>
-      </c>
-      <c r="L456" s="45" t="s">
+      <c r="K456">
+        <v>2</v>
+      </c>
+      <c r="L456" t="s">
         <v>27</v>
       </c>
-      <c r="M456" s="46">
+      <c r="M456" s="42">
         <v>338.1</v>
       </c>
-      <c r="N456" s="45">
+      <c r="N456">
         <v>383.62</v>
       </c>
-      <c r="O456" s="45">
+      <c r="O456">
         <v>7.77</v>
       </c>
       <c r="R456" t="s">
@@ -21497,46 +21491,46 @@
       </c>
     </row>
     <row r="457" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A457" s="45" t="s">
+      <c r="A457" t="s">
         <v>31</v>
       </c>
       <c r="B457" s="15">
         <v>45914.674305555556</v>
       </c>
-      <c r="D457" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E457" s="45">
-        <v>1</v>
-      </c>
-      <c r="F457" s="45">
-        <v>1</v>
-      </c>
-      <c r="G457" s="45" t="s">
+      <c r="D457" t="s">
+        <v>5</v>
+      </c>
+      <c r="E457">
+        <v>1</v>
+      </c>
+      <c r="F457">
+        <v>1</v>
+      </c>
+      <c r="G457" t="s">
         <v>12</v>
       </c>
-      <c r="H457" s="45">
+      <c r="H457">
         <v>132</v>
       </c>
-      <c r="I457" s="45">
-        <v>2</v>
-      </c>
-      <c r="J457" s="45" t="s">
+      <c r="I457">
+        <v>2</v>
+      </c>
+      <c r="J457" t="s">
         <v>36</v>
       </c>
-      <c r="K457" s="45">
-        <v>2</v>
-      </c>
-      <c r="L457" s="45" t="s">
+      <c r="K457">
+        <v>2</v>
+      </c>
+      <c r="L457" t="s">
         <v>27</v>
       </c>
-      <c r="M457" s="46">
+      <c r="M457" s="42">
         <v>614.29999999999995</v>
       </c>
-      <c r="N457" s="45">
+      <c r="N457">
         <v>357.41</v>
       </c>
-      <c r="O457" s="45">
+      <c r="O457">
         <v>4.03</v>
       </c>
       <c r="R457" t="s">
@@ -21544,46 +21538,46 @@
       </c>
     </row>
     <row r="458" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A458" s="45" t="s">
+      <c r="A458" t="s">
         <v>31</v>
       </c>
       <c r="B458" s="15">
         <v>45914.674305555556</v>
       </c>
-      <c r="D458" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E458" s="45">
-        <v>1</v>
-      </c>
-      <c r="F458" s="45">
-        <v>1</v>
-      </c>
-      <c r="G458" s="45" t="s">
+      <c r="D458" t="s">
+        <v>5</v>
+      </c>
+      <c r="E458">
+        <v>1</v>
+      </c>
+      <c r="F458">
+        <v>1</v>
+      </c>
+      <c r="G458" t="s">
         <v>12</v>
       </c>
-      <c r="H458" s="45">
+      <c r="H458">
         <v>133</v>
       </c>
-      <c r="I458" s="45">
+      <c r="I458">
         <v>3</v>
       </c>
-      <c r="J458" s="45" t="s">
+      <c r="J458" t="s">
         <v>36</v>
       </c>
-      <c r="K458" s="45">
-        <v>2</v>
-      </c>
-      <c r="L458" s="45" t="s">
+      <c r="K458">
+        <v>2</v>
+      </c>
+      <c r="L458" t="s">
         <v>27</v>
       </c>
-      <c r="M458" s="46">
+      <c r="M458" s="42">
         <v>295.3</v>
       </c>
-      <c r="N458" s="45">
+      <c r="N458">
         <v>339.53</v>
       </c>
-      <c r="O458" s="45">
+      <c r="O458">
         <v>11.31</v>
       </c>
       <c r="R458" t="s">
@@ -21591,7 +21585,7 @@
       </c>
     </row>
     <row r="459" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A459" s="45" t="s">
+      <c r="A459" t="s">
         <v>31</v>
       </c>
       <c r="B459" s="15">
@@ -21600,34 +21594,34 @@
       <c r="C459">
         <v>0</v>
       </c>
-      <c r="D459" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E459" s="45">
-        <v>1</v>
-      </c>
-      <c r="F459" s="45">
-        <v>1</v>
-      </c>
-      <c r="G459" s="45" t="s">
+      <c r="D459" t="s">
+        <v>5</v>
+      </c>
+      <c r="E459">
+        <v>1</v>
+      </c>
+      <c r="F459">
+        <v>1</v>
+      </c>
+      <c r="G459" t="s">
         <v>34</v>
       </c>
-      <c r="H459" s="45">
+      <c r="H459">
         <v>134</v>
       </c>
-      <c r="I459" s="45">
-        <v>1</v>
-      </c>
-      <c r="J459" s="45" t="s">
+      <c r="I459">
+        <v>1</v>
+      </c>
+      <c r="J459" t="s">
         <v>37</v>
       </c>
-      <c r="K459" s="45">
-        <v>1</v>
-      </c>
-      <c r="L459" s="45" t="s">
+      <c r="K459">
+        <v>1</v>
+      </c>
+      <c r="L459" t="s">
         <v>7</v>
       </c>
-      <c r="M459" s="46">
+      <c r="M459" s="42">
         <v>454.8</v>
       </c>
       <c r="R459" t="s">
@@ -21635,7 +21629,7 @@
       </c>
     </row>
     <row r="460" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A460" s="45" t="s">
+      <c r="A460" t="s">
         <v>31</v>
       </c>
       <c r="B460" s="15">
@@ -21644,34 +21638,34 @@
       <c r="C460">
         <v>0</v>
       </c>
-      <c r="D460" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E460" s="45">
-        <v>1</v>
-      </c>
-      <c r="F460" s="45">
-        <v>1</v>
-      </c>
-      <c r="G460" s="45" t="s">
+      <c r="D460" t="s">
+        <v>5</v>
+      </c>
+      <c r="E460">
+        <v>1</v>
+      </c>
+      <c r="F460">
+        <v>1</v>
+      </c>
+      <c r="G460" t="s">
         <v>34</v>
       </c>
-      <c r="H460" s="45">
+      <c r="H460">
         <v>135</v>
       </c>
-      <c r="I460" s="45">
-        <v>2</v>
-      </c>
-      <c r="J460" s="45" t="s">
+      <c r="I460">
+        <v>2</v>
+      </c>
+      <c r="J460" t="s">
         <v>37</v>
       </c>
-      <c r="K460" s="45">
-        <v>1</v>
-      </c>
-      <c r="L460" s="45" t="s">
+      <c r="K460">
+        <v>1</v>
+      </c>
+      <c r="L460" t="s">
         <v>7</v>
       </c>
-      <c r="M460" s="46">
+      <c r="M460" s="42">
         <v>493.1</v>
       </c>
       <c r="R460" t="s">
@@ -21679,7 +21673,7 @@
       </c>
     </row>
     <row r="461" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A461" s="45" t="s">
+      <c r="A461" t="s">
         <v>31</v>
       </c>
       <c r="B461" s="15">
@@ -21688,34 +21682,34 @@
       <c r="C461">
         <v>0</v>
       </c>
-      <c r="D461" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E461" s="45">
-        <v>1</v>
-      </c>
-      <c r="F461" s="45">
-        <v>1</v>
-      </c>
-      <c r="G461" s="45" t="s">
+      <c r="D461" t="s">
+        <v>5</v>
+      </c>
+      <c r="E461">
+        <v>1</v>
+      </c>
+      <c r="F461">
+        <v>1</v>
+      </c>
+      <c r="G461" t="s">
         <v>34</v>
       </c>
-      <c r="H461" s="45">
+      <c r="H461">
         <v>136</v>
       </c>
-      <c r="I461" s="45">
+      <c r="I461">
         <v>3</v>
       </c>
-      <c r="J461" s="45" t="s">
+      <c r="J461" t="s">
         <v>37</v>
       </c>
-      <c r="K461" s="45">
-        <v>1</v>
-      </c>
-      <c r="L461" s="45" t="s">
+      <c r="K461">
+        <v>1</v>
+      </c>
+      <c r="L461" t="s">
         <v>7</v>
       </c>
-      <c r="M461" s="46">
+      <c r="M461" s="42">
         <v>386.7</v>
       </c>
       <c r="R461" t="s">
@@ -21723,40 +21717,40 @@
       </c>
     </row>
     <row r="462" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A462" s="45" t="s">
+      <c r="A462" t="s">
         <v>31</v>
       </c>
       <c r="B462" s="15">
         <v>45915.59097222222</v>
       </c>
-      <c r="D462" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E462" s="45">
-        <v>1</v>
-      </c>
-      <c r="F462" s="45">
-        <v>1</v>
-      </c>
-      <c r="G462" s="45" t="s">
+      <c r="D462" t="s">
+        <v>5</v>
+      </c>
+      <c r="E462">
+        <v>1</v>
+      </c>
+      <c r="F462">
+        <v>1</v>
+      </c>
+      <c r="G462" t="s">
         <v>34</v>
       </c>
-      <c r="H462" s="45">
+      <c r="H462">
         <v>134</v>
       </c>
-      <c r="I462" s="45">
-        <v>1</v>
-      </c>
-      <c r="J462" s="45" t="s">
+      <c r="I462">
+        <v>1</v>
+      </c>
+      <c r="J462" t="s">
         <v>37</v>
       </c>
-      <c r="K462" s="45">
-        <v>2</v>
-      </c>
-      <c r="L462" s="45" t="s">
+      <c r="K462">
+        <v>2</v>
+      </c>
+      <c r="L462" t="s">
         <v>7</v>
       </c>
-      <c r="M462" s="46">
+      <c r="M462" s="42">
         <v>455.3</v>
       </c>
       <c r="R462" t="s">
@@ -21764,40 +21758,40 @@
       </c>
     </row>
     <row r="463" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A463" s="45" t="s">
+      <c r="A463" t="s">
         <v>31</v>
       </c>
       <c r="B463" s="15">
         <v>45915.594444444447</v>
       </c>
-      <c r="D463" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E463" s="45">
-        <v>1</v>
-      </c>
-      <c r="F463" s="45">
-        <v>1</v>
-      </c>
-      <c r="G463" s="45" t="s">
+      <c r="D463" t="s">
+        <v>5</v>
+      </c>
+      <c r="E463">
+        <v>1</v>
+      </c>
+      <c r="F463">
+        <v>1</v>
+      </c>
+      <c r="G463" t="s">
         <v>34</v>
       </c>
-      <c r="H463" s="45">
+      <c r="H463">
         <v>135</v>
       </c>
-      <c r="I463" s="45">
-        <v>2</v>
-      </c>
-      <c r="J463" s="45" t="s">
+      <c r="I463">
+        <v>2</v>
+      </c>
+      <c r="J463" t="s">
         <v>37</v>
       </c>
-      <c r="K463" s="45">
-        <v>2</v>
-      </c>
-      <c r="L463" s="45" t="s">
+      <c r="K463">
+        <v>2</v>
+      </c>
+      <c r="L463" t="s">
         <v>7</v>
       </c>
-      <c r="M463" s="46">
+      <c r="M463" s="42">
         <v>490.5</v>
       </c>
       <c r="R463" t="s">
@@ -21805,40 +21799,40 @@
       </c>
     </row>
     <row r="464" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A464" s="45" t="s">
+      <c r="A464" t="s">
         <v>31</v>
       </c>
       <c r="B464" s="15">
         <v>45915.59652777778</v>
       </c>
-      <c r="D464" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E464" s="45">
-        <v>1</v>
-      </c>
-      <c r="F464" s="45">
-        <v>1</v>
-      </c>
-      <c r="G464" s="45" t="s">
+      <c r="D464" t="s">
+        <v>5</v>
+      </c>
+      <c r="E464">
+        <v>1</v>
+      </c>
+      <c r="F464">
+        <v>1</v>
+      </c>
+      <c r="G464" t="s">
         <v>34</v>
       </c>
-      <c r="H464" s="45">
+      <c r="H464">
         <v>136</v>
       </c>
-      <c r="I464" s="45">
+      <c r="I464">
         <v>3</v>
       </c>
-      <c r="J464" s="45" t="s">
+      <c r="J464" t="s">
         <v>37</v>
       </c>
-      <c r="K464" s="45">
-        <v>2</v>
-      </c>
-      <c r="L464" s="45" t="s">
+      <c r="K464">
+        <v>2</v>
+      </c>
+      <c r="L464" t="s">
         <v>7</v>
       </c>
-      <c r="M464" s="46">
+      <c r="M464" s="42">
         <v>440.4</v>
       </c>
       <c r="R464" t="s">
@@ -21846,46 +21840,46 @@
       </c>
     </row>
     <row r="465" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A465" s="45" t="s">
+      <c r="A465" t="s">
         <v>31</v>
       </c>
       <c r="B465" s="15">
         <v>45915.593055555553</v>
       </c>
-      <c r="D465" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E465" s="45">
-        <v>1</v>
-      </c>
-      <c r="F465" s="45">
-        <v>1</v>
-      </c>
-      <c r="G465" s="45" t="s">
+      <c r="D465" t="s">
+        <v>5</v>
+      </c>
+      <c r="E465">
+        <v>1</v>
+      </c>
+      <c r="F465">
+        <v>1</v>
+      </c>
+      <c r="G465" t="s">
         <v>34</v>
       </c>
-      <c r="H465" s="45">
+      <c r="H465">
         <v>134</v>
       </c>
-      <c r="I465" s="45">
-        <v>1</v>
-      </c>
-      <c r="J465" s="45" t="s">
+      <c r="I465">
+        <v>1</v>
+      </c>
+      <c r="J465" t="s">
         <v>37</v>
       </c>
-      <c r="K465" s="45">
-        <v>2</v>
-      </c>
-      <c r="L465" s="45" t="s">
+      <c r="K465">
+        <v>2</v>
+      </c>
+      <c r="L465" t="s">
         <v>27</v>
       </c>
-      <c r="M465" s="46">
+      <c r="M465" s="42">
         <v>391</v>
       </c>
-      <c r="N465" s="45">
+      <c r="N465">
         <v>847.61</v>
       </c>
-      <c r="O465" s="45">
+      <c r="O465">
         <v>8.36</v>
       </c>
       <c r="R465" t="s">
@@ -21893,46 +21887,46 @@
       </c>
     </row>
     <row r="466" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A466" s="45" t="s">
+      <c r="A466" t="s">
         <v>31</v>
       </c>
       <c r="B466" s="15">
         <v>45915.59652777778</v>
       </c>
-      <c r="D466" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E466" s="45">
-        <v>1</v>
-      </c>
-      <c r="F466" s="45">
-        <v>1</v>
-      </c>
-      <c r="G466" s="45" t="s">
+      <c r="D466" t="s">
+        <v>5</v>
+      </c>
+      <c r="E466">
+        <v>1</v>
+      </c>
+      <c r="F466">
+        <v>1</v>
+      </c>
+      <c r="G466" t="s">
         <v>34</v>
       </c>
-      <c r="H466" s="45">
+      <c r="H466">
         <v>135</v>
       </c>
-      <c r="I466" s="45">
-        <v>2</v>
-      </c>
-      <c r="J466" s="45" t="s">
+      <c r="I466">
+        <v>2</v>
+      </c>
+      <c r="J466" t="s">
         <v>37</v>
       </c>
-      <c r="K466" s="45">
-        <v>2</v>
-      </c>
-      <c r="L466" s="45" t="s">
+      <c r="K466">
+        <v>2</v>
+      </c>
+      <c r="L466" t="s">
         <v>27</v>
       </c>
-      <c r="M466" s="46">
+      <c r="M466" s="42">
         <v>421.1</v>
       </c>
-      <c r="N466" s="45">
+      <c r="N466">
         <v>488.5</v>
       </c>
-      <c r="O466" s="45">
+      <c r="O466">
         <v>7.18</v>
       </c>
       <c r="R466" t="s">
@@ -21940,46 +21934,46 @@
       </c>
     </row>
     <row r="467" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A467" s="45" t="s">
+      <c r="A467" t="s">
         <v>31</v>
       </c>
       <c r="B467" s="15">
         <v>45915.598611111112</v>
       </c>
-      <c r="D467" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E467" s="45">
-        <v>1</v>
-      </c>
-      <c r="F467" s="45">
-        <v>1</v>
-      </c>
-      <c r="G467" s="45" t="s">
+      <c r="D467" t="s">
+        <v>5</v>
+      </c>
+      <c r="E467">
+        <v>1</v>
+      </c>
+      <c r="F467">
+        <v>1</v>
+      </c>
+      <c r="G467" t="s">
         <v>34</v>
       </c>
-      <c r="H467" s="45">
+      <c r="H467">
         <v>136</v>
       </c>
-      <c r="I467" s="45">
+      <c r="I467">
         <v>3</v>
       </c>
-      <c r="J467" s="45" t="s">
+      <c r="J467" t="s">
         <v>37</v>
       </c>
-      <c r="K467" s="45">
-        <v>2</v>
-      </c>
-      <c r="L467" s="45" t="s">
+      <c r="K467">
+        <v>2</v>
+      </c>
+      <c r="L467" t="s">
         <v>27</v>
       </c>
-      <c r="M467" s="46">
+      <c r="M467" s="42">
         <v>409.7</v>
       </c>
-      <c r="N467" s="45">
+      <c r="N467">
         <v>842.32</v>
       </c>
-      <c r="O467" s="45">
+      <c r="O467">
         <v>5.0599999999999996</v>
       </c>
       <c r="R467" t="s">
@@ -21987,7 +21981,7 @@
       </c>
     </row>
     <row r="468" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A468" s="45" t="s">
+      <c r="A468" t="s">
         <v>31</v>
       </c>
       <c r="B468" s="15">
@@ -21996,34 +21990,34 @@
       <c r="C468">
         <v>0</v>
       </c>
-      <c r="D468" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E468" s="45">
-        <v>1</v>
-      </c>
-      <c r="F468" s="45">
-        <v>1</v>
-      </c>
-      <c r="G468" s="45" t="s">
+      <c r="D468" t="s">
+        <v>5</v>
+      </c>
+      <c r="E468">
+        <v>1</v>
+      </c>
+      <c r="F468">
+        <v>1</v>
+      </c>
+      <c r="G468" t="s">
         <v>34</v>
       </c>
-      <c r="H468" s="45">
+      <c r="H468">
         <v>137</v>
       </c>
-      <c r="I468" s="45">
-        <v>1</v>
-      </c>
-      <c r="J468" s="45" t="s">
+      <c r="I468">
+        <v>1</v>
+      </c>
+      <c r="J468" t="s">
         <v>38</v>
       </c>
-      <c r="K468" s="45">
-        <v>1</v>
-      </c>
-      <c r="L468" s="45" t="s">
+      <c r="K468">
+        <v>1</v>
+      </c>
+      <c r="L468" t="s">
         <v>7</v>
       </c>
-      <c r="M468" s="46">
+      <c r="M468" s="42">
         <v>392.4</v>
       </c>
       <c r="R468" t="s">
@@ -22031,7 +22025,7 @@
       </c>
     </row>
     <row r="469" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A469" s="45" t="s">
+      <c r="A469" t="s">
         <v>31</v>
       </c>
       <c r="B469" s="15">
@@ -22040,34 +22034,34 @@
       <c r="C469">
         <v>0</v>
       </c>
-      <c r="D469" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E469" s="45">
-        <v>1</v>
-      </c>
-      <c r="F469" s="45">
-        <v>1</v>
-      </c>
-      <c r="G469" s="45" t="s">
+      <c r="D469" t="s">
+        <v>5</v>
+      </c>
+      <c r="E469">
+        <v>1</v>
+      </c>
+      <c r="F469">
+        <v>1</v>
+      </c>
+      <c r="G469" t="s">
         <v>34</v>
       </c>
-      <c r="H469" s="45">
+      <c r="H469">
         <v>138</v>
       </c>
-      <c r="I469" s="45">
-        <v>2</v>
-      </c>
-      <c r="J469" s="45" t="s">
+      <c r="I469">
+        <v>2</v>
+      </c>
+      <c r="J469" t="s">
         <v>38</v>
       </c>
-      <c r="K469" s="45">
-        <v>1</v>
-      </c>
-      <c r="L469" s="45" t="s">
+      <c r="K469">
+        <v>1</v>
+      </c>
+      <c r="L469" t="s">
         <v>7</v>
       </c>
-      <c r="M469" s="46">
+      <c r="M469" s="42">
         <v>414.4</v>
       </c>
       <c r="R469" t="s">
@@ -22075,7 +22069,7 @@
       </c>
     </row>
     <row r="470" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A470" s="45" t="s">
+      <c r="A470" t="s">
         <v>31</v>
       </c>
       <c r="B470" s="15">
@@ -22084,34 +22078,34 @@
       <c r="C470">
         <v>0</v>
       </c>
-      <c r="D470" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E470" s="45">
-        <v>1</v>
-      </c>
-      <c r="F470" s="45">
-        <v>1</v>
-      </c>
-      <c r="G470" s="45" t="s">
+      <c r="D470" t="s">
+        <v>5</v>
+      </c>
+      <c r="E470">
+        <v>1</v>
+      </c>
+      <c r="F470">
+        <v>1</v>
+      </c>
+      <c r="G470" t="s">
         <v>34</v>
       </c>
-      <c r="H470" s="45">
+      <c r="H470">
         <v>139</v>
       </c>
-      <c r="I470" s="45">
+      <c r="I470">
         <v>3</v>
       </c>
-      <c r="J470" s="45" t="s">
+      <c r="J470" t="s">
         <v>38</v>
       </c>
-      <c r="K470" s="45">
-        <v>1</v>
-      </c>
-      <c r="L470" s="45" t="s">
+      <c r="K470">
+        <v>1</v>
+      </c>
+      <c r="L470" t="s">
         <v>7</v>
       </c>
-      <c r="M470" s="46">
+      <c r="M470" s="42">
         <v>467.4</v>
       </c>
       <c r="R470" t="s">
@@ -22119,40 +22113,40 @@
       </c>
     </row>
     <row r="471" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A471" s="45" t="s">
+      <c r="A471" t="s">
         <v>31</v>
       </c>
       <c r="B471" s="15">
         <v>45917.55972222222</v>
       </c>
-      <c r="D471" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E471" s="45">
-        <v>1</v>
-      </c>
-      <c r="F471" s="45">
-        <v>1</v>
-      </c>
-      <c r="G471" s="45" t="s">
+      <c r="D471" t="s">
+        <v>5</v>
+      </c>
+      <c r="E471">
+        <v>1</v>
+      </c>
+      <c r="F471">
+        <v>1</v>
+      </c>
+      <c r="G471" t="s">
         <v>34</v>
       </c>
-      <c r="H471" s="45">
+      <c r="H471">
         <v>137</v>
       </c>
-      <c r="I471" s="45">
-        <v>1</v>
-      </c>
-      <c r="J471" s="45" t="s">
+      <c r="I471">
+        <v>1</v>
+      </c>
+      <c r="J471" t="s">
         <v>38</v>
       </c>
-      <c r="K471" s="45">
-        <v>2</v>
-      </c>
-      <c r="L471" s="45" t="s">
+      <c r="K471">
+        <v>2</v>
+      </c>
+      <c r="L471" t="s">
         <v>7</v>
       </c>
-      <c r="M471" s="46">
+      <c r="M471" s="42">
         <v>520.9</v>
       </c>
       <c r="R471" t="s">
@@ -22160,40 +22154,40 @@
       </c>
     </row>
     <row r="472" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A472" s="45" t="s">
+      <c r="A472" t="s">
         <v>31</v>
       </c>
       <c r="B472" s="15">
         <v>45917.5625</v>
       </c>
-      <c r="D472" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E472" s="45">
-        <v>1</v>
-      </c>
-      <c r="F472" s="45">
-        <v>1</v>
-      </c>
-      <c r="G472" s="45" t="s">
+      <c r="D472" t="s">
+        <v>5</v>
+      </c>
+      <c r="E472">
+        <v>1</v>
+      </c>
+      <c r="F472">
+        <v>1</v>
+      </c>
+      <c r="G472" t="s">
         <v>34</v>
       </c>
-      <c r="H472" s="45">
+      <c r="H472">
         <v>138</v>
       </c>
-      <c r="I472" s="45">
-        <v>2</v>
-      </c>
-      <c r="J472" s="45" t="s">
+      <c r="I472">
+        <v>2</v>
+      </c>
+      <c r="J472" t="s">
         <v>38</v>
       </c>
-      <c r="K472" s="45">
-        <v>2</v>
-      </c>
-      <c r="L472" s="45" t="s">
+      <c r="K472">
+        <v>2</v>
+      </c>
+      <c r="L472" t="s">
         <v>7</v>
       </c>
-      <c r="M472" s="46">
+      <c r="M472" s="42">
         <v>503.1</v>
       </c>
       <c r="R472" t="s">
@@ -22201,40 +22195,40 @@
       </c>
     </row>
     <row r="473" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A473" s="45" t="s">
+      <c r="A473" t="s">
         <v>31</v>
       </c>
-      <c r="B473" s="47">
+      <c r="B473" s="43">
         <v>45917.564583333333</v>
       </c>
-      <c r="D473" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E473" s="45">
-        <v>1</v>
-      </c>
-      <c r="F473" s="45">
-        <v>1</v>
-      </c>
-      <c r="G473" s="45" t="s">
+      <c r="D473" t="s">
+        <v>5</v>
+      </c>
+      <c r="E473">
+        <v>1</v>
+      </c>
+      <c r="F473">
+        <v>1</v>
+      </c>
+      <c r="G473" t="s">
         <v>34</v>
       </c>
-      <c r="H473" s="45">
+      <c r="H473">
         <v>139</v>
       </c>
-      <c r="I473" s="45">
+      <c r="I473">
         <v>3</v>
       </c>
-      <c r="J473" s="45" t="s">
+      <c r="J473" t="s">
         <v>38</v>
       </c>
-      <c r="K473" s="45">
-        <v>2</v>
-      </c>
-      <c r="L473" s="45" t="s">
+      <c r="K473">
+        <v>2</v>
+      </c>
+      <c r="L473" t="s">
         <v>7</v>
       </c>
-      <c r="M473" s="46">
+      <c r="M473" s="42">
         <v>512.1</v>
       </c>
       <c r="R473" t="s">
@@ -22242,46 +22236,46 @@
       </c>
     </row>
     <row r="474" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A474" s="45" t="s">
+      <c r="A474" t="s">
         <v>31</v>
       </c>
       <c r="B474" s="15">
         <v>45917.561805555553</v>
       </c>
-      <c r="D474" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E474" s="45">
-        <v>1</v>
-      </c>
-      <c r="F474" s="45">
-        <v>1</v>
-      </c>
-      <c r="G474" s="45" t="s">
+      <c r="D474" t="s">
+        <v>5</v>
+      </c>
+      <c r="E474">
+        <v>1</v>
+      </c>
+      <c r="F474">
+        <v>1</v>
+      </c>
+      <c r="G474" t="s">
         <v>34</v>
       </c>
-      <c r="H474" s="45">
+      <c r="H474">
         <v>137</v>
       </c>
-      <c r="I474" s="45">
-        <v>1</v>
-      </c>
-      <c r="J474" s="45" t="s">
+      <c r="I474">
+        <v>1</v>
+      </c>
+      <c r="J474" t="s">
         <v>38</v>
       </c>
-      <c r="K474" s="45">
-        <v>2</v>
-      </c>
-      <c r="L474" s="45" t="s">
+      <c r="K474">
+        <v>2</v>
+      </c>
+      <c r="L474" t="s">
         <v>27</v>
       </c>
-      <c r="M474" s="46">
+      <c r="M474" s="42">
         <v>466.7</v>
       </c>
-      <c r="N474" s="45">
+      <c r="N474">
         <v>628.16999999999996</v>
       </c>
-      <c r="O474" s="45">
+      <c r="O474">
         <v>21.12</v>
       </c>
       <c r="R474" t="s">
@@ -22289,46 +22283,46 @@
       </c>
     </row>
     <row r="475" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A475" s="45" t="s">
+      <c r="A475" t="s">
         <v>31</v>
       </c>
       <c r="B475" s="15">
         <v>45917.563888888886</v>
       </c>
-      <c r="D475" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E475" s="45">
-        <v>1</v>
-      </c>
-      <c r="F475" s="45">
-        <v>1</v>
-      </c>
-      <c r="G475" s="45" t="s">
+      <c r="D475" t="s">
+        <v>5</v>
+      </c>
+      <c r="E475">
+        <v>1</v>
+      </c>
+      <c r="F475">
+        <v>1</v>
+      </c>
+      <c r="G475" t="s">
         <v>34</v>
       </c>
-      <c r="H475" s="45">
+      <c r="H475">
         <v>138</v>
       </c>
-      <c r="I475" s="45">
-        <v>2</v>
-      </c>
-      <c r="J475" s="45" t="s">
+      <c r="I475">
+        <v>2</v>
+      </c>
+      <c r="J475" t="s">
         <v>38</v>
       </c>
-      <c r="K475" s="45">
-        <v>2</v>
-      </c>
-      <c r="L475" s="45" t="s">
+      <c r="K475">
+        <v>2</v>
+      </c>
+      <c r="L475" t="s">
         <v>27</v>
       </c>
-      <c r="M475" s="46">
+      <c r="M475" s="42">
         <v>463.1</v>
       </c>
-      <c r="N475" s="45">
+      <c r="N475">
         <v>683.91</v>
       </c>
-      <c r="O475" s="45">
+      <c r="O475">
         <v>5.76</v>
       </c>
       <c r="R475" t="s">
@@ -22336,46 +22330,46 @@
       </c>
     </row>
     <row r="476" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A476" s="45" t="s">
+      <c r="A476" t="s">
         <v>31</v>
       </c>
-      <c r="B476" s="47">
+      <c r="B476" s="43">
         <v>45917.565972222219</v>
       </c>
-      <c r="D476" s="45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E476" s="45">
-        <v>1</v>
-      </c>
-      <c r="F476" s="45">
-        <v>1</v>
-      </c>
-      <c r="G476" s="45" t="s">
+      <c r="D476" t="s">
+        <v>5</v>
+      </c>
+      <c r="E476">
+        <v>1</v>
+      </c>
+      <c r="F476">
+        <v>1</v>
+      </c>
+      <c r="G476" t="s">
         <v>34</v>
       </c>
-      <c r="H476" s="45">
+      <c r="H476">
         <v>139</v>
       </c>
-      <c r="I476" s="45">
+      <c r="I476">
         <v>3</v>
       </c>
-      <c r="J476" s="45" t="s">
+      <c r="J476" t="s">
         <v>38</v>
       </c>
-      <c r="K476" s="45">
-        <v>2</v>
-      </c>
-      <c r="L476" s="45" t="s">
+      <c r="K476">
+        <v>2</v>
+      </c>
+      <c r="L476" t="s">
         <v>27</v>
       </c>
-      <c r="M476" s="46">
+      <c r="M476" s="42">
         <v>485.5</v>
       </c>
-      <c r="N476" s="45">
+      <c r="N476">
         <v>569.12</v>
       </c>
-      <c r="O476" s="45">
+      <c r="O476">
         <v>5.07</v>
       </c>
       <c r="R476" t="s">
@@ -22383,7 +22377,7 @@
       </c>
     </row>
     <row r="477" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A477" s="45" t="s">
+      <c r="A477" t="s">
         <v>31</v>
       </c>
       <c r="B477" s="15">
@@ -22392,34 +22386,34 @@
       <c r="C477">
         <v>0</v>
       </c>
-      <c r="D477" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E477" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F477" s="45">
-        <v>1</v>
-      </c>
-      <c r="G477" s="45" t="s">
+      <c r="D477" t="s">
+        <v>6</v>
+      </c>
+      <c r="E477">
+        <v>0.1</v>
+      </c>
+      <c r="F477">
+        <v>1</v>
+      </c>
+      <c r="G477" t="s">
         <v>35</v>
       </c>
-      <c r="H477" s="45">
+      <c r="H477">
         <v>140</v>
       </c>
-      <c r="I477" s="45">
-        <v>1</v>
-      </c>
-      <c r="J477" s="45" t="s">
+      <c r="I477">
+        <v>1</v>
+      </c>
+      <c r="J477" t="s">
         <v>38</v>
       </c>
-      <c r="K477" s="45">
-        <v>1</v>
-      </c>
-      <c r="L477" s="45" t="s">
+      <c r="K477">
+        <v>1</v>
+      </c>
+      <c r="L477" t="s">
         <v>7</v>
       </c>
-      <c r="M477" s="46">
+      <c r="M477" s="42">
         <v>490.8</v>
       </c>
       <c r="R477" t="s">
@@ -22427,7 +22421,7 @@
       </c>
     </row>
     <row r="478" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A478" s="45" t="s">
+      <c r="A478" t="s">
         <v>31</v>
       </c>
       <c r="B478" s="15">
@@ -22436,34 +22430,34 @@
       <c r="C478">
         <v>0</v>
       </c>
-      <c r="D478" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E478" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F478" s="45">
-        <v>1</v>
-      </c>
-      <c r="G478" s="45" t="s">
+      <c r="D478" t="s">
+        <v>6</v>
+      </c>
+      <c r="E478">
+        <v>0.1</v>
+      </c>
+      <c r="F478">
+        <v>1</v>
+      </c>
+      <c r="G478" t="s">
         <v>35</v>
       </c>
-      <c r="H478" s="45">
+      <c r="H478">
         <v>141</v>
       </c>
-      <c r="I478" s="45">
-        <v>2</v>
-      </c>
-      <c r="J478" s="45" t="s">
+      <c r="I478">
+        <v>2</v>
+      </c>
+      <c r="J478" t="s">
         <v>38</v>
       </c>
-      <c r="K478" s="45">
-        <v>1</v>
-      </c>
-      <c r="L478" s="45" t="s">
+      <c r="K478">
+        <v>1</v>
+      </c>
+      <c r="L478" t="s">
         <v>7</v>
       </c>
-      <c r="M478" s="46">
+      <c r="M478" s="42">
         <v>368.3</v>
       </c>
       <c r="R478" t="s">
@@ -22471,7 +22465,7 @@
       </c>
     </row>
     <row r="479" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A479" s="45" t="s">
+      <c r="A479" t="s">
         <v>31</v>
       </c>
       <c r="B479" s="15">
@@ -22480,34 +22474,34 @@
       <c r="C479">
         <v>0</v>
       </c>
-      <c r="D479" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E479" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F479" s="45">
-        <v>1</v>
-      </c>
-      <c r="G479" s="45" t="s">
+      <c r="D479" t="s">
+        <v>6</v>
+      </c>
+      <c r="E479">
+        <v>0.1</v>
+      </c>
+      <c r="F479">
+        <v>1</v>
+      </c>
+      <c r="G479" t="s">
         <v>35</v>
       </c>
-      <c r="H479" s="45">
+      <c r="H479">
         <v>142</v>
       </c>
-      <c r="I479" s="45">
+      <c r="I479">
         <v>3</v>
       </c>
-      <c r="J479" s="45" t="s">
+      <c r="J479" t="s">
         <v>38</v>
       </c>
-      <c r="K479" s="45">
-        <v>1</v>
-      </c>
-      <c r="L479" s="45" t="s">
+      <c r="K479">
+        <v>1</v>
+      </c>
+      <c r="L479" t="s">
         <v>7</v>
       </c>
-      <c r="M479" s="46">
+      <c r="M479" s="42">
         <v>376.3</v>
       </c>
       <c r="R479" t="s">
@@ -22515,40 +22509,40 @@
       </c>
     </row>
     <row r="480" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A480" s="45" t="s">
+      <c r="A480" t="s">
         <v>31</v>
       </c>
       <c r="B480" s="15">
         <v>45917.566666666666</v>
       </c>
-      <c r="D480" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E480" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F480" s="45">
-        <v>1</v>
-      </c>
-      <c r="G480" s="45" t="s">
+      <c r="D480" t="s">
+        <v>6</v>
+      </c>
+      <c r="E480">
+        <v>0.1</v>
+      </c>
+      <c r="F480">
+        <v>1</v>
+      </c>
+      <c r="G480" t="s">
         <v>35</v>
       </c>
-      <c r="H480" s="45">
+      <c r="H480">
         <v>140</v>
       </c>
-      <c r="I480" s="45">
-        <v>1</v>
-      </c>
-      <c r="J480" s="45" t="s">
+      <c r="I480">
+        <v>1</v>
+      </c>
+      <c r="J480" t="s">
         <v>38</v>
       </c>
-      <c r="K480" s="45">
-        <v>2</v>
-      </c>
-      <c r="L480" s="45" t="s">
+      <c r="K480">
+        <v>2</v>
+      </c>
+      <c r="L480" t="s">
         <v>7</v>
       </c>
-      <c r="M480" s="46">
+      <c r="M480" s="42">
         <v>366.2</v>
       </c>
       <c r="R480" t="s">
@@ -22556,40 +22550,40 @@
       </c>
     </row>
     <row r="481" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A481" s="45" t="s">
+      <c r="A481" t="s">
         <v>31</v>
       </c>
       <c r="B481" s="15">
         <v>45917.568055555559</v>
       </c>
-      <c r="D481" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E481" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F481" s="45">
-        <v>1</v>
-      </c>
-      <c r="G481" s="45" t="s">
+      <c r="D481" t="s">
+        <v>6</v>
+      </c>
+      <c r="E481">
+        <v>0.1</v>
+      </c>
+      <c r="F481">
+        <v>1</v>
+      </c>
+      <c r="G481" t="s">
         <v>35</v>
       </c>
-      <c r="H481" s="45">
+      <c r="H481">
         <v>141</v>
       </c>
-      <c r="I481" s="45">
-        <v>2</v>
-      </c>
-      <c r="J481" s="45" t="s">
+      <c r="I481">
+        <v>2</v>
+      </c>
+      <c r="J481" t="s">
         <v>38</v>
       </c>
-      <c r="K481" s="45">
-        <v>2</v>
-      </c>
-      <c r="L481" s="45" t="s">
+      <c r="K481">
+        <v>2</v>
+      </c>
+      <c r="L481" t="s">
         <v>7</v>
       </c>
-      <c r="M481" s="46">
+      <c r="M481" s="42">
         <v>319.10000000000002</v>
       </c>
       <c r="R481" t="s">
@@ -22597,40 +22591,40 @@
       </c>
     </row>
     <row r="482" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A482" s="45" t="s">
+      <c r="A482" t="s">
         <v>31</v>
       </c>
-      <c r="B482" s="47">
+      <c r="B482" s="43">
         <v>45917.570138888892</v>
       </c>
-      <c r="D482" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E482" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F482" s="45">
-        <v>1</v>
-      </c>
-      <c r="G482" s="45" t="s">
+      <c r="D482" t="s">
+        <v>6</v>
+      </c>
+      <c r="E482">
+        <v>0.1</v>
+      </c>
+      <c r="F482">
+        <v>1</v>
+      </c>
+      <c r="G482" t="s">
         <v>35</v>
       </c>
-      <c r="H482" s="45">
+      <c r="H482">
         <v>142</v>
       </c>
-      <c r="I482" s="45">
+      <c r="I482">
         <v>3</v>
       </c>
-      <c r="J482" s="45" t="s">
+      <c r="J482" t="s">
         <v>38</v>
       </c>
-      <c r="K482" s="45">
-        <v>2</v>
-      </c>
-      <c r="L482" s="45" t="s">
+      <c r="K482">
+        <v>2</v>
+      </c>
+      <c r="L482" t="s">
         <v>7</v>
       </c>
-      <c r="M482" s="46">
+      <c r="M482" s="42">
         <v>309.2</v>
       </c>
       <c r="R482" t="s">
@@ -22638,46 +22632,46 @@
       </c>
     </row>
     <row r="483" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A483" s="45" t="s">
+      <c r="A483" t="s">
         <v>31</v>
       </c>
       <c r="B483" s="15">
         <v>45917.567361111112</v>
       </c>
-      <c r="D483" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E483" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F483" s="45">
-        <v>1</v>
-      </c>
-      <c r="G483" s="45" t="s">
+      <c r="D483" t="s">
+        <v>6</v>
+      </c>
+      <c r="E483">
+        <v>0.1</v>
+      </c>
+      <c r="F483">
+        <v>1</v>
+      </c>
+      <c r="G483" t="s">
         <v>35</v>
       </c>
-      <c r="H483" s="45">
+      <c r="H483">
         <v>140</v>
       </c>
-      <c r="I483" s="45">
-        <v>1</v>
-      </c>
-      <c r="J483" s="45" t="s">
+      <c r="I483">
+        <v>1</v>
+      </c>
+      <c r="J483" t="s">
         <v>38</v>
       </c>
-      <c r="K483" s="45">
-        <v>2</v>
-      </c>
-      <c r="L483" s="45" t="s">
+      <c r="K483">
+        <v>2</v>
+      </c>
+      <c r="L483" t="s">
         <v>27</v>
       </c>
-      <c r="M483" s="46">
+      <c r="M483" s="42">
         <v>356.1</v>
       </c>
-      <c r="N483" s="45">
+      <c r="N483">
         <v>5.64</v>
       </c>
-      <c r="O483" s="45">
+      <c r="O483">
         <v>632.45000000000005</v>
       </c>
       <c r="R483" t="s">
@@ -22685,46 +22679,46 @@
       </c>
     </row>
     <row r="484" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A484" s="45" t="s">
+      <c r="A484" t="s">
         <v>31</v>
       </c>
       <c r="B484" s="15">
         <v>45917.568749999999</v>
       </c>
-      <c r="D484" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E484" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F484" s="45">
-        <v>1</v>
-      </c>
-      <c r="G484" s="45" t="s">
+      <c r="D484" t="s">
+        <v>6</v>
+      </c>
+      <c r="E484">
+        <v>0.1</v>
+      </c>
+      <c r="F484">
+        <v>1</v>
+      </c>
+      <c r="G484" t="s">
         <v>35</v>
       </c>
-      <c r="H484" s="45">
+      <c r="H484">
         <v>141</v>
       </c>
-      <c r="I484" s="45">
-        <v>2</v>
-      </c>
-      <c r="J484" s="45" t="s">
+      <c r="I484">
+        <v>2</v>
+      </c>
+      <c r="J484" t="s">
         <v>38</v>
       </c>
-      <c r="K484" s="45">
-        <v>2</v>
-      </c>
-      <c r="L484" s="45" t="s">
+      <c r="K484">
+        <v>2</v>
+      </c>
+      <c r="L484" t="s">
         <v>27</v>
       </c>
-      <c r="M484" s="46">
+      <c r="M484" s="42">
         <v>303.39999999999998</v>
       </c>
-      <c r="N484" s="45">
+      <c r="N484">
         <v>3.31</v>
       </c>
-      <c r="O484" s="45">
+      <c r="O484">
         <v>571.04999999999995</v>
       </c>
       <c r="R484" t="s">
@@ -22732,46 +22726,46 @@
       </c>
     </row>
     <row r="485" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A485" s="45" t="s">
+      <c r="A485" t="s">
         <v>31</v>
       </c>
-      <c r="B485" s="47">
+      <c r="B485" s="43">
         <v>45917.571527777778</v>
       </c>
-      <c r="D485" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E485" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F485" s="45">
-        <v>1</v>
-      </c>
-      <c r="G485" s="45" t="s">
+      <c r="D485" t="s">
+        <v>6</v>
+      </c>
+      <c r="E485">
+        <v>0.1</v>
+      </c>
+      <c r="F485">
+        <v>1</v>
+      </c>
+      <c r="G485" t="s">
         <v>35</v>
       </c>
-      <c r="H485" s="45">
+      <c r="H485">
         <v>142</v>
       </c>
-      <c r="I485" s="45">
+      <c r="I485">
         <v>3</v>
       </c>
-      <c r="J485" s="45" t="s">
+      <c r="J485" t="s">
         <v>38</v>
       </c>
-      <c r="K485" s="45">
-        <v>2</v>
-      </c>
-      <c r="L485" s="45" t="s">
+      <c r="K485">
+        <v>2</v>
+      </c>
+      <c r="L485" t="s">
         <v>27</v>
       </c>
-      <c r="M485" s="46">
+      <c r="M485" s="42">
         <v>286.39999999999998</v>
       </c>
-      <c r="N485" s="45">
+      <c r="N485">
         <v>3.32</v>
       </c>
-      <c r="O485" s="45">
+      <c r="O485">
         <v>721.38</v>
       </c>
       <c r="R485" t="s">
@@ -22779,7 +22773,7 @@
       </c>
     </row>
     <row r="486" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A486" s="45" t="s">
+      <c r="A486" t="s">
         <v>31</v>
       </c>
       <c r="B486" s="15">
@@ -22788,34 +22782,34 @@
       <c r="C486">
         <v>0</v>
       </c>
-      <c r="D486" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E486" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F486" s="45">
-        <v>1</v>
-      </c>
-      <c r="G486" s="45" t="s">
+      <c r="D486" t="s">
+        <v>6</v>
+      </c>
+      <c r="E486">
+        <v>0.1</v>
+      </c>
+      <c r="F486">
+        <v>1</v>
+      </c>
+      <c r="G486" t="s">
         <v>35</v>
       </c>
-      <c r="H486" s="45">
+      <c r="H486">
         <v>143</v>
       </c>
-      <c r="I486" s="45">
-        <v>1</v>
-      </c>
-      <c r="J486" s="45" t="s">
+      <c r="I486">
+        <v>1</v>
+      </c>
+      <c r="J486" t="s">
         <v>39</v>
       </c>
-      <c r="K486" s="45">
-        <v>1</v>
-      </c>
-      <c r="L486" s="45" t="s">
+      <c r="K486">
+        <v>1</v>
+      </c>
+      <c r="L486" t="s">
         <v>7</v>
       </c>
-      <c r="M486" s="46">
+      <c r="M486" s="42">
         <v>408.8</v>
       </c>
       <c r="R486" t="s">
@@ -22823,7 +22817,7 @@
       </c>
     </row>
     <row r="487" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A487" s="45" t="s">
+      <c r="A487" t="s">
         <v>31</v>
       </c>
       <c r="B487" s="15">
@@ -22832,34 +22826,34 @@
       <c r="C487">
         <v>0</v>
       </c>
-      <c r="D487" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E487" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F487" s="45">
-        <v>1</v>
-      </c>
-      <c r="G487" s="45" t="s">
+      <c r="D487" t="s">
+        <v>6</v>
+      </c>
+      <c r="E487">
+        <v>0.1</v>
+      </c>
+      <c r="F487">
+        <v>1</v>
+      </c>
+      <c r="G487" t="s">
         <v>35</v>
       </c>
-      <c r="H487" s="45">
+      <c r="H487">
         <v>144</v>
       </c>
-      <c r="I487" s="45">
-        <v>2</v>
-      </c>
-      <c r="J487" s="45" t="s">
+      <c r="I487">
+        <v>2</v>
+      </c>
+      <c r="J487" t="s">
         <v>39</v>
       </c>
-      <c r="K487" s="45">
-        <v>1</v>
-      </c>
-      <c r="L487" s="45" t="s">
+      <c r="K487">
+        <v>1</v>
+      </c>
+      <c r="L487" t="s">
         <v>7</v>
       </c>
-      <c r="M487" s="46">
+      <c r="M487" s="42">
         <v>373.2</v>
       </c>
       <c r="R487" t="s">
@@ -22867,43 +22861,43 @@
       </c>
     </row>
     <row r="488" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A488" s="45" t="s">
+      <c r="A488" t="s">
         <v>31</v>
       </c>
-      <c r="B488" s="47">
+      <c r="B488" s="43">
         <v>45914.5625</v>
       </c>
       <c r="C488">
         <v>0</v>
       </c>
-      <c r="D488" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E488" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F488" s="45">
-        <v>1</v>
-      </c>
-      <c r="G488" s="45" t="s">
+      <c r="D488" t="s">
+        <v>6</v>
+      </c>
+      <c r="E488">
+        <v>0.1</v>
+      </c>
+      <c r="F488">
+        <v>1</v>
+      </c>
+      <c r="G488" t="s">
         <v>14</v>
       </c>
-      <c r="H488" s="45">
+      <c r="H488">
         <v>145</v>
       </c>
-      <c r="I488" s="45">
+      <c r="I488">
         <v>3</v>
       </c>
-      <c r="J488" s="45" t="s">
+      <c r="J488" t="s">
         <v>39</v>
       </c>
-      <c r="K488" s="45">
-        <v>1</v>
-      </c>
-      <c r="L488" s="45" t="s">
+      <c r="K488">
+        <v>1</v>
+      </c>
+      <c r="L488" t="s">
         <v>7</v>
       </c>
-      <c r="M488" s="46">
+      <c r="M488" s="42">
         <v>416.5</v>
       </c>
       <c r="R488" t="s">
@@ -22911,40 +22905,40 @@
       </c>
     </row>
     <row r="489" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A489" s="45" t="s">
+      <c r="A489" t="s">
         <v>31</v>
       </c>
       <c r="B489" s="15">
         <v>45921.564583333333</v>
       </c>
-      <c r="D489" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E489" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F489" s="45">
-        <v>1</v>
-      </c>
-      <c r="G489" s="45" t="s">
+      <c r="D489" t="s">
+        <v>6</v>
+      </c>
+      <c r="E489">
+        <v>0.1</v>
+      </c>
+      <c r="F489">
+        <v>1</v>
+      </c>
+      <c r="G489" t="s">
         <v>35</v>
       </c>
-      <c r="H489" s="45">
+      <c r="H489">
         <v>143</v>
       </c>
-      <c r="I489" s="45">
-        <v>1</v>
-      </c>
-      <c r="J489" s="45" t="s">
+      <c r="I489">
+        <v>1</v>
+      </c>
+      <c r="J489" t="s">
         <v>39</v>
       </c>
-      <c r="K489" s="45">
-        <v>2</v>
-      </c>
-      <c r="L489" s="45" t="s">
+      <c r="K489">
+        <v>2</v>
+      </c>
+      <c r="L489" t="s">
         <v>7</v>
       </c>
-      <c r="M489" s="46">
+      <c r="M489" s="42">
         <v>293.60000000000002</v>
       </c>
       <c r="R489" t="s">
@@ -22952,40 +22946,40 @@
       </c>
     </row>
     <row r="490" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A490" s="45" t="s">
+      <c r="A490" t="s">
         <v>31</v>
       </c>
       <c r="B490" s="15">
         <v>45921.56527777778</v>
       </c>
-      <c r="D490" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E490" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F490" s="45">
-        <v>1</v>
-      </c>
-      <c r="G490" s="45" t="s">
+      <c r="D490" t="s">
+        <v>6</v>
+      </c>
+      <c r="E490">
+        <v>0.1</v>
+      </c>
+      <c r="F490">
+        <v>1</v>
+      </c>
+      <c r="G490" t="s">
         <v>35</v>
       </c>
-      <c r="H490" s="45">
+      <c r="H490">
         <v>144</v>
       </c>
-      <c r="I490" s="45">
-        <v>2</v>
-      </c>
-      <c r="J490" s="45" t="s">
+      <c r="I490">
+        <v>2</v>
+      </c>
+      <c r="J490" t="s">
         <v>39</v>
       </c>
-      <c r="K490" s="45">
-        <v>2</v>
-      </c>
-      <c r="L490" s="45" t="s">
+      <c r="K490">
+        <v>2</v>
+      </c>
+      <c r="L490" t="s">
         <v>7</v>
       </c>
-      <c r="M490" s="46">
+      <c r="M490" s="42">
         <v>284.39999999999998</v>
       </c>
       <c r="R490" t="s">
@@ -22993,40 +22987,40 @@
       </c>
     </row>
     <row r="491" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A491" s="45" t="s">
+      <c r="A491" t="s">
         <v>31</v>
       </c>
       <c r="B491" s="15">
         <v>45921.568055555559</v>
       </c>
-      <c r="D491" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E491" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F491" s="45">
-        <v>1</v>
-      </c>
-      <c r="G491" s="45" t="s">
+      <c r="D491" t="s">
+        <v>6</v>
+      </c>
+      <c r="E491">
+        <v>0.1</v>
+      </c>
+      <c r="F491">
+        <v>1</v>
+      </c>
+      <c r="G491" t="s">
         <v>14</v>
       </c>
-      <c r="H491" s="45">
+      <c r="H491">
         <v>145</v>
       </c>
-      <c r="I491" s="45">
+      <c r="I491">
         <v>3</v>
       </c>
-      <c r="J491" s="45" t="s">
+      <c r="J491" t="s">
         <v>39</v>
       </c>
-      <c r="K491" s="45">
-        <v>2</v>
-      </c>
-      <c r="L491" s="45" t="s">
+      <c r="K491">
+        <v>2</v>
+      </c>
+      <c r="L491" t="s">
         <v>7</v>
       </c>
-      <c r="M491" s="46">
+      <c r="M491" s="42">
         <v>267.5</v>
       </c>
       <c r="R491" t="s">
@@ -23034,46 +23028,46 @@
       </c>
     </row>
     <row r="492" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A492" s="45" t="s">
+      <c r="A492" t="s">
         <v>31</v>
       </c>
       <c r="B492" s="15">
         <v>45921.564930555556</v>
       </c>
-      <c r="D492" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E492" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F492" s="45">
-        <v>1</v>
-      </c>
-      <c r="G492" s="45" t="s">
+      <c r="D492" t="s">
+        <v>6</v>
+      </c>
+      <c r="E492">
+        <v>0.1</v>
+      </c>
+      <c r="F492">
+        <v>1</v>
+      </c>
+      <c r="G492" t="s">
         <v>35</v>
       </c>
-      <c r="H492" s="45">
+      <c r="H492">
         <v>143</v>
       </c>
-      <c r="I492" s="45">
-        <v>1</v>
-      </c>
-      <c r="J492" s="45" t="s">
+      <c r="I492">
+        <v>1</v>
+      </c>
+      <c r="J492" t="s">
         <v>39</v>
       </c>
-      <c r="K492" s="45">
-        <v>2</v>
-      </c>
-      <c r="L492" s="45" t="s">
+      <c r="K492">
+        <v>2</v>
+      </c>
+      <c r="L492" t="s">
         <v>27</v>
       </c>
-      <c r="M492" s="46">
+      <c r="M492" s="42">
         <v>293.60000000000002</v>
       </c>
-      <c r="N492" s="45">
+      <c r="N492">
         <v>6.22</v>
       </c>
-      <c r="O492" s="45">
+      <c r="O492">
         <v>757.25</v>
       </c>
       <c r="R492" t="s">
@@ -23081,46 +23075,46 @@
       </c>
     </row>
     <row r="493" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A493" s="45" t="s">
+      <c r="A493" t="s">
         <v>31</v>
       </c>
       <c r="B493" s="15">
         <v>45921.565972222219</v>
       </c>
-      <c r="D493" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E493" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F493" s="45">
-        <v>1</v>
-      </c>
-      <c r="G493" s="45" t="s">
+      <c r="D493" t="s">
+        <v>6</v>
+      </c>
+      <c r="E493">
+        <v>0.1</v>
+      </c>
+      <c r="F493">
+        <v>1</v>
+      </c>
+      <c r="G493" t="s">
         <v>35</v>
       </c>
-      <c r="H493" s="45">
+      <c r="H493">
         <v>144</v>
       </c>
-      <c r="I493" s="45">
-        <v>2</v>
-      </c>
-      <c r="J493" s="45" t="s">
+      <c r="I493">
+        <v>2</v>
+      </c>
+      <c r="J493" t="s">
         <v>39</v>
       </c>
-      <c r="K493" s="45">
-        <v>2</v>
-      </c>
-      <c r="L493" s="45" t="s">
+      <c r="K493">
+        <v>2</v>
+      </c>
+      <c r="L493" t="s">
         <v>27</v>
       </c>
-      <c r="M493" s="46">
+      <c r="M493" s="42">
         <v>263.7</v>
       </c>
-      <c r="N493" s="45">
+      <c r="N493">
         <v>3.31</v>
       </c>
-      <c r="O493" s="45">
+      <c r="O493">
         <v>949.76</v>
       </c>
       <c r="R493" t="s">
@@ -23128,46 +23122,46 @@
       </c>
     </row>
     <row r="494" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A494" s="45" t="s">
+      <c r="A494" t="s">
         <v>31</v>
       </c>
       <c r="B494" s="15">
         <v>45921.568749999999</v>
       </c>
-      <c r="D494" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E494" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F494" s="45">
-        <v>1</v>
-      </c>
-      <c r="G494" s="45" t="s">
+      <c r="D494" t="s">
+        <v>6</v>
+      </c>
+      <c r="E494">
+        <v>0.1</v>
+      </c>
+      <c r="F494">
+        <v>1</v>
+      </c>
+      <c r="G494" t="s">
         <v>14</v>
       </c>
-      <c r="H494" s="45">
+      <c r="H494">
         <v>145</v>
       </c>
-      <c r="I494" s="45">
+      <c r="I494">
         <v>3</v>
       </c>
-      <c r="J494" s="45" t="s">
+      <c r="J494" t="s">
         <v>39</v>
       </c>
-      <c r="K494" s="45">
-        <v>2</v>
-      </c>
-      <c r="L494" s="45" t="s">
+      <c r="K494">
+        <v>2</v>
+      </c>
+      <c r="L494" t="s">
         <v>27</v>
       </c>
-      <c r="M494" s="46">
+      <c r="M494" s="42">
         <v>267.5</v>
       </c>
-      <c r="N494" s="45">
+      <c r="N494">
         <v>3.4</v>
       </c>
-      <c r="O494" s="45">
+      <c r="O494">
         <v>900.55</v>
       </c>
       <c r="R494" t="s">
@@ -23175,7 +23169,7 @@
       </c>
     </row>
     <row r="495" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A495" s="45" t="s">
+      <c r="A495" t="s">
         <v>31</v>
       </c>
       <c r="B495" s="15">
@@ -23184,34 +23178,34 @@
       <c r="C495">
         <v>0</v>
       </c>
-      <c r="D495" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E495" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F495" s="45">
-        <v>1</v>
-      </c>
-      <c r="G495" s="45" t="s">
+      <c r="D495" t="s">
+        <v>6</v>
+      </c>
+      <c r="E495">
+        <v>0.1</v>
+      </c>
+      <c r="F495">
+        <v>1</v>
+      </c>
+      <c r="G495" t="s">
         <v>14</v>
       </c>
-      <c r="H495" s="45">
+      <c r="H495">
         <v>146</v>
       </c>
-      <c r="I495" s="45">
-        <v>1</v>
-      </c>
-      <c r="J495" s="45" t="s">
+      <c r="I495">
+        <v>1</v>
+      </c>
+      <c r="J495" t="s">
         <v>40</v>
       </c>
-      <c r="K495" s="45">
-        <v>1</v>
-      </c>
-      <c r="L495" s="45" t="s">
+      <c r="K495">
+        <v>1</v>
+      </c>
+      <c r="L495" t="s">
         <v>7</v>
       </c>
-      <c r="M495" s="46">
+      <c r="M495" s="42">
         <v>430.8</v>
       </c>
       <c r="R495" t="s">
@@ -23219,7 +23213,7 @@
       </c>
     </row>
     <row r="496" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A496" s="45" t="s">
+      <c r="A496" t="s">
         <v>31</v>
       </c>
       <c r="B496" s="15">
@@ -23228,34 +23222,34 @@
       <c r="C496">
         <v>0</v>
       </c>
-      <c r="D496" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E496" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F496" s="45">
-        <v>1</v>
-      </c>
-      <c r="G496" s="45" t="s">
+      <c r="D496" t="s">
+        <v>6</v>
+      </c>
+      <c r="E496">
+        <v>0.1</v>
+      </c>
+      <c r="F496">
+        <v>1</v>
+      </c>
+      <c r="G496" t="s">
         <v>35</v>
       </c>
-      <c r="H496" s="45">
+      <c r="H496">
         <v>147</v>
       </c>
-      <c r="I496" s="45">
-        <v>2</v>
-      </c>
-      <c r="J496" s="45" t="s">
+      <c r="I496">
+        <v>2</v>
+      </c>
+      <c r="J496" t="s">
         <v>40</v>
       </c>
-      <c r="K496" s="45">
-        <v>1</v>
-      </c>
-      <c r="L496" s="45" t="s">
+      <c r="K496">
+        <v>1</v>
+      </c>
+      <c r="L496" t="s">
         <v>7</v>
       </c>
-      <c r="M496" s="46">
+      <c r="M496" s="42">
         <v>350</v>
       </c>
       <c r="R496" t="s">
@@ -23263,43 +23257,43 @@
       </c>
     </row>
     <row r="497" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A497" s="45" t="s">
+      <c r="A497" t="s">
         <v>31</v>
       </c>
-      <c r="B497" s="47">
+      <c r="B497" s="43">
         <v>45914.564583333333</v>
       </c>
       <c r="C497">
         <v>0</v>
       </c>
-      <c r="D497" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E497" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F497" s="45">
-        <v>1</v>
-      </c>
-      <c r="G497" s="45" t="s">
+      <c r="D497" t="s">
+        <v>6</v>
+      </c>
+      <c r="E497">
+        <v>0.1</v>
+      </c>
+      <c r="F497">
+        <v>1</v>
+      </c>
+      <c r="G497" t="s">
         <v>35</v>
       </c>
-      <c r="H497" s="45">
+      <c r="H497">
         <v>148</v>
       </c>
-      <c r="I497" s="45">
+      <c r="I497">
         <v>3</v>
       </c>
-      <c r="J497" s="45" t="s">
+      <c r="J497" t="s">
         <v>40</v>
       </c>
-      <c r="K497" s="45">
-        <v>1</v>
-      </c>
-      <c r="L497" s="45" t="s">
+      <c r="K497">
+        <v>1</v>
+      </c>
+      <c r="L497" t="s">
         <v>7</v>
       </c>
-      <c r="M497" s="46">
+      <c r="M497" s="42">
         <v>410.8</v>
       </c>
       <c r="R497" t="s">
@@ -23307,46 +23301,46 @@
       </c>
     </row>
     <row r="498" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A498" s="45" t="s">
+      <c r="A498" t="s">
         <v>31</v>
       </c>
       <c r="B498" s="15">
         <v>45928.552083333336</v>
       </c>
-      <c r="D498" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E498" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F498" s="45">
-        <v>1</v>
-      </c>
-      <c r="G498" s="45" t="s">
+      <c r="D498" t="s">
+        <v>6</v>
+      </c>
+      <c r="E498">
+        <v>0.1</v>
+      </c>
+      <c r="F498">
+        <v>1</v>
+      </c>
+      <c r="G498" t="s">
         <v>14</v>
       </c>
-      <c r="H498" s="45">
+      <c r="H498">
         <v>146</v>
       </c>
-      <c r="I498" s="45">
-        <v>1</v>
-      </c>
-      <c r="J498" s="45" t="s">
+      <c r="I498">
+        <v>1</v>
+      </c>
+      <c r="J498" t="s">
         <v>40</v>
       </c>
-      <c r="K498" s="45">
-        <v>2</v>
-      </c>
-      <c r="L498" s="45" t="s">
+      <c r="K498">
+        <v>2</v>
+      </c>
+      <c r="L498" t="s">
         <v>27</v>
       </c>
-      <c r="M498" s="46">
+      <c r="M498" s="42">
         <v>279</v>
       </c>
-      <c r="N498" s="45">
+      <c r="N498">
         <v>3.03</v>
       </c>
-      <c r="O498" s="45">
+      <c r="O498">
         <v>1319.62</v>
       </c>
       <c r="R498" t="s">
@@ -23354,46 +23348,46 @@
       </c>
     </row>
     <row r="499" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A499" s="45" t="s">
+      <c r="A499" t="s">
         <v>31</v>
       </c>
-      <c r="B499" s="47">
+      <c r="B499" s="43">
         <v>45928.553472222222</v>
       </c>
-      <c r="D499" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E499" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F499" s="45">
-        <v>1</v>
-      </c>
-      <c r="G499" s="45" t="s">
+      <c r="D499" t="s">
+        <v>6</v>
+      </c>
+      <c r="E499">
+        <v>0.1</v>
+      </c>
+      <c r="F499">
+        <v>1</v>
+      </c>
+      <c r="G499" t="s">
         <v>35</v>
       </c>
-      <c r="H499" s="45">
+      <c r="H499">
         <v>147</v>
       </c>
-      <c r="I499" s="45">
-        <v>2</v>
-      </c>
-      <c r="J499" s="45" t="s">
+      <c r="I499">
+        <v>2</v>
+      </c>
+      <c r="J499" t="s">
         <v>40</v>
       </c>
-      <c r="K499" s="45">
-        <v>2</v>
-      </c>
-      <c r="L499" s="45" t="s">
+      <c r="K499">
+        <v>2</v>
+      </c>
+      <c r="L499" t="s">
         <v>27</v>
       </c>
-      <c r="M499" s="46">
+      <c r="M499" s="42">
         <v>222.2</v>
       </c>
-      <c r="N499" s="45">
+      <c r="N499">
         <v>3.59</v>
       </c>
-      <c r="O499" s="45">
+      <c r="O499">
         <v>860.11</v>
       </c>
       <c r="R499" t="s">
@@ -23401,46 +23395,46 @@
       </c>
     </row>
     <row r="500" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
-      <c r="A500" s="45" t="s">
+      <c r="A500" t="s">
         <v>31</v>
       </c>
-      <c r="B500" s="47">
+      <c r="B500" s="43">
         <v>45928.554861111108</v>
       </c>
-      <c r="D500" s="45" t="s">
-        <v>6</v>
-      </c>
-      <c r="E500" s="45">
-        <v>0.1</v>
-      </c>
-      <c r="F500" s="45">
-        <v>1</v>
-      </c>
-      <c r="G500" s="45" t="s">
+      <c r="D500" t="s">
+        <v>6</v>
+      </c>
+      <c r="E500">
+        <v>0.1</v>
+      </c>
+      <c r="F500">
+        <v>1</v>
+      </c>
+      <c r="G500" t="s">
         <v>35</v>
       </c>
-      <c r="H500" s="45">
+      <c r="H500">
         <v>148</v>
       </c>
-      <c r="I500" s="45">
+      <c r="I500">
         <v>3</v>
       </c>
-      <c r="J500" s="45" t="s">
+      <c r="J500" t="s">
         <v>40</v>
       </c>
-      <c r="K500" s="45">
-        <v>2</v>
-      </c>
-      <c r="L500" s="45" t="s">
+      <c r="K500">
+        <v>2</v>
+      </c>
+      <c r="L500" t="s">
         <v>27</v>
       </c>
-      <c r="M500" s="46">
+      <c r="M500" s="42">
         <v>265.8</v>
       </c>
-      <c r="N500" s="45">
+      <c r="N500">
         <v>3.05</v>
       </c>
-      <c r="O500" s="45">
+      <c r="O500">
         <v>1208.82</v>
       </c>
       <c r="R500" t="s">
@@ -23448,52 +23442,19 @@
       </c>
     </row>
     <row r="501" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A501" s="45"/>
       <c r="B501" s="15"/>
-      <c r="D501" s="45"/>
-      <c r="E501" s="45"/>
-      <c r="F501" s="45"/>
-      <c r="G501" s="45"/>
-      <c r="H501" s="45"/>
-      <c r="I501" s="45"/>
-      <c r="J501" s="45"/>
-      <c r="K501" s="45"/>
     </row>
     <row r="502" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A502" s="45"/>
-      <c r="B502" s="47"/>
-      <c r="D502" s="45"/>
-      <c r="E502" s="45"/>
-      <c r="F502" s="45"/>
-      <c r="G502" s="45"/>
-      <c r="H502" s="45"/>
-      <c r="I502" s="45"/>
-      <c r="J502" s="45"/>
-      <c r="K502" s="45"/>
+      <c r="B502" s="43"/>
     </row>
     <row r="503" spans="1:18" x14ac:dyDescent="0.2">
-      <c r="A503" s="45"/>
-      <c r="B503" s="47"/>
-      <c r="D503" s="45"/>
-      <c r="E503" s="45"/>
-      <c r="F503" s="45"/>
-      <c r="G503" s="45"/>
-      <c r="H503" s="45"/>
-      <c r="I503" s="45"/>
-      <c r="J503" s="45"/>
-      <c r="K503" s="45"/>
+      <c r="B503" s="43"/>
     </row>
   </sheetData>
-  <autoFilter ref="B1:R500" xr:uid="{AE06E5C9-F603-BD4A-AB05-F790F7B78C9A}">
-    <filterColumn colId="2">
+  <autoFilter ref="A1:R500" xr:uid="{AE06E5C9-F603-BD4A-AB05-F790F7B78C9A}">
+    <filterColumn colId="17">
       <filters>
-        <filter val="EPX"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="6">
-      <filters>
-        <filter val="105"/>
-        <filter val="106"/>
+        <filter val="No"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -23525,59 +23486,59 @@
     <col min="2" max="2" width="15.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="44" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="44" t="s">
+    <row r="1" spans="1:18" s="41" customFormat="1" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="44" t="s">
+      <c r="B1" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="44" t="s">
+      <c r="C1" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="44" t="s">
+      <c r="D1" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="44" t="s">
+      <c r="E1" s="41" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" s="41" t="s">
         <v>10</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="44" t="s">
+      <c r="H1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="44" t="s">
+      <c r="I1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="44" t="s">
-        <v>2</v>
-      </c>
-      <c r="K1" s="44" t="s">
+      <c r="J1" s="41" t="s">
+        <v>2</v>
+      </c>
+      <c r="K1" s="41" t="s">
         <v>28</v>
       </c>
-      <c r="L1" s="44" t="s">
+      <c r="L1" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="44" t="s">
+      <c r="M1" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="N1" s="44" t="s">
+      <c r="N1" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="O1" s="44" t="s">
+      <c r="O1" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="P1" s="44" t="s">
+      <c r="P1" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="Q1" s="44" t="s">
+      <c r="Q1" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="R1" s="44" t="s">
+      <c r="R1" s="41" t="s">
         <v>21</v>
       </c>
     </row>

--- a/data/Data_TK_long.xlsx
+++ b/data/Data_TK_long.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/lisagollot/Library/CloudStorage/OneDrive-Personnel/Documents/0_These/0_RepoGit/Ew-Mix-TK/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21381663-6892-6C4E-9AA7-43EFEE8ED752}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CDFCEC0-6860-7C48-A261-5714353951AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{63D67807-0DCA-1F4C-A29E-414A7CCA2C56}"/>
   </bookViews>
@@ -3467,7 +3467,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>30</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>30</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="66" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>30</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>30</v>
       </c>
@@ -4145,7 +4145,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>30</v>
       </c>
@@ -4192,7 +4192,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>30</v>
       </c>
@@ -4239,7 +4239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>30</v>
       </c>
@@ -4287,7 +4287,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>30</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>30</v>
       </c>
@@ -4382,7 +4382,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>30</v>
       </c>
@@ -4429,7 +4429,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="74" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>30</v>
       </c>
@@ -4477,7 +4477,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>30</v>
       </c>
@@ -4525,7 +4525,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="76" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>30</v>
       </c>
@@ -4572,7 +4572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="77" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>30</v>
       </c>
@@ -4619,7 +4619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>30</v>
       </c>
@@ -4667,7 +4667,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>30</v>
       </c>
@@ -4715,7 +4715,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>30</v>
       </c>
@@ -4762,7 +4762,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>30</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="82" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -4857,7 +4857,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="83" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>30</v>
       </c>
@@ -4905,7 +4905,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>30</v>
       </c>
@@ -4952,7 +4952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="85" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>30</v>
       </c>
@@ -4999,7 +4999,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>30</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
         <v>30</v>
       </c>
@@ -5095,7 +5095,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="88" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
         <v>30</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="89" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
         <v>30</v>
       </c>
@@ -5189,7 +5189,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="90" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
         <v>30</v>
       </c>
@@ -5285,7 +5285,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
         <v>30</v>
       </c>
@@ -5332,7 +5332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="93" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
         <v>30</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
         <v>30</v>
       </c>
@@ -5427,7 +5427,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
         <v>30</v>
       </c>
@@ -5475,7 +5475,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
         <v>30</v>
       </c>
@@ -5522,7 +5522,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
         <v>30</v>
       </c>
@@ -5569,7 +5569,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="98" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
         <v>30</v>
       </c>
@@ -5617,7 +5617,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
         <v>30</v>
       </c>
@@ -5665,7 +5665,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
         <v>30</v>
       </c>
@@ -5712,7 +5712,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="101" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
         <v>30</v>
       </c>
@@ -5759,7 +5759,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
         <v>30</v>
       </c>
@@ -5807,7 +5807,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
         <v>30</v>
       </c>
@@ -5855,7 +5855,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
         <v>30</v>
       </c>
@@ -5902,7 +5902,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
         <v>30</v>
       </c>
@@ -5949,7 +5949,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="106" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
         <v>30</v>
       </c>
@@ -5997,7 +5997,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
         <v>30</v>
       </c>
@@ -6045,7 +6045,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
         <v>30</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="109" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
         <v>30</v>
       </c>
@@ -6139,7 +6139,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
         <v>30</v>
       </c>
@@ -6187,7 +6187,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
         <v>30</v>
       </c>
@@ -6235,7 +6235,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
         <v>30</v>
       </c>
@@ -6282,7 +6282,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
         <v>30</v>
       </c>
@@ -6329,7 +6329,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="114" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
         <v>30</v>
       </c>
@@ -6377,7 +6377,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
         <v>30</v>
       </c>
@@ -6425,7 +6425,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
         <v>30</v>
       </c>
@@ -6472,7 +6472,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="117" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
         <v>30</v>
       </c>
@@ -6519,7 +6519,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
         <v>30</v>
       </c>
@@ -6567,7 +6567,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
         <v>30</v>
       </c>
@@ -6615,7 +6615,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
         <v>30</v>
       </c>
@@ -6662,7 +6662,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
         <v>30</v>
       </c>
@@ -6709,7 +6709,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="122" spans="1:18" s="1" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:18" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
         <v>30</v>
       </c>
@@ -6757,7 +6757,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
         <v>30</v>
       </c>
@@ -6805,7 +6805,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
         <v>30</v>
       </c>
@@ -6852,7 +6852,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="125" spans="1:18" s="2" customFormat="1" hidden="1" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:18" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
         <v>30</v>
       </c>
@@ -6899,7 +6899,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
         <v>30</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
         <v>30</v>
       </c>
@@ -6995,7 +6995,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
         <v>30</v>
       </c>
@@ -7042,7 +7042,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="129" spans="1:18" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>30</v>
       </c>
@@ -9243,7 +9243,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A182" t="s">
         <v>30</v>
       </c>
@@ -9283,7 +9283,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A183" t="s">
         <v>30</v>
       </c>
@@ -10563,7 +10563,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
         <v>30</v>
       </c>
@@ -10605,7 +10605,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
         <v>30</v>
       </c>
@@ -11067,7 +11067,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A226" t="s">
         <v>30</v>
       </c>
@@ -11109,7 +11109,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="227" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A227" t="s">
         <v>30</v>
       </c>
@@ -11151,7 +11151,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A228" t="s">
         <v>30</v>
       </c>
@@ -11193,7 +11193,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A229" t="s">
         <v>30</v>
       </c>
@@ -11235,7 +11235,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A230" t="s">
         <v>30</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A231" t="s">
         <v>30</v>
       </c>
@@ -11319,7 +11319,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A232" t="s">
         <v>30</v>
       </c>
@@ -11361,7 +11361,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A233" t="s">
         <v>30</v>
       </c>
@@ -11403,7 +11403,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A234" t="s">
         <v>30</v>
       </c>
@@ -11445,7 +11445,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A235" t="s">
         <v>30</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A236" t="s">
         <v>30</v>
       </c>
@@ -11529,7 +11529,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A237" t="s">
         <v>30</v>
       </c>
@@ -11571,7 +11571,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A238" t="s">
         <v>30</v>
       </c>
@@ -11613,7 +11613,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A239" t="s">
         <v>30</v>
       </c>
@@ -11655,7 +11655,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A240" t="s">
         <v>30</v>
       </c>
@@ -11697,7 +11697,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A241" t="s">
         <v>30</v>
       </c>
@@ -11742,7 +11742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A242" t="s">
         <v>30</v>
       </c>
@@ -11784,7 +11784,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A243" t="s">
         <v>30</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A244" t="s">
         <v>30</v>
       </c>
@@ -11868,7 +11868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A245" t="s">
         <v>30</v>
       </c>
@@ -11910,7 +11910,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A246" t="s">
         <v>30</v>
       </c>
@@ -11952,7 +11952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A247" t="s">
         <v>30</v>
       </c>
@@ -11994,7 +11994,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A248" t="s">
         <v>30</v>
       </c>
@@ -12036,7 +12036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A249" t="s">
         <v>30</v>
       </c>
@@ -12081,7 +12081,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A250" t="s">
         <v>30</v>
       </c>
@@ -12165,7 +12165,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A252" t="s">
         <v>30</v>
       </c>
@@ -12207,7 +12207,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A253" t="s">
         <v>30</v>
       </c>
@@ -12249,7 +12249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A254" t="s">
         <v>30</v>
       </c>
@@ -12291,7 +12291,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="255" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A255" t="s">
         <v>30</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="256" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A256" t="s">
         <v>30</v>
       </c>
@@ -12375,7 +12375,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="257" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A257" t="s">
         <v>30</v>
       </c>
@@ -12420,7 +12420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="258" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A258" t="s">
         <v>30</v>
       </c>
@@ -12460,7 +12460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="259" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A259" t="s">
         <v>30</v>
       </c>
@@ -12500,7 +12500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A260" t="s">
         <v>30</v>
       </c>
@@ -12540,7 +12540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A261" t="s">
         <v>30</v>
       </c>
@@ -12580,7 +12580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="262" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A262" t="s">
         <v>30</v>
       </c>
@@ -12620,7 +12620,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="263" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A263" t="s">
         <v>30</v>
       </c>
@@ -12660,7 +12660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="264" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A264" t="s">
         <v>30</v>
       </c>
@@ -12700,7 +12700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="265" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A265" t="s">
         <v>30</v>
       </c>
@@ -12740,7 +12740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="266" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A266" t="s">
         <v>30</v>
       </c>
@@ -12780,7 +12780,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A267" t="s">
         <v>30</v>
       </c>
@@ -12820,7 +12820,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A268" t="s">
         <v>30</v>
       </c>
@@ -12860,7 +12860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A269" t="s">
         <v>30</v>
       </c>
@@ -12900,7 +12900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A270" t="s">
         <v>30</v>
       </c>
@@ -12940,7 +12940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A271" t="s">
         <v>30</v>
       </c>
@@ -12980,7 +12980,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A272" t="s">
         <v>30</v>
       </c>
@@ -13020,7 +13020,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A273" t="s">
         <v>30</v>
       </c>
@@ -13060,7 +13060,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A274" t="s">
         <v>30</v>
       </c>
@@ -13100,7 +13100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A275" t="s">
         <v>30</v>
       </c>
@@ -13140,7 +13140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="276" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A276" t="s">
         <v>30</v>
       </c>
@@ -13180,7 +13180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A277" t="s">
         <v>30</v>
       </c>
@@ -13220,7 +13220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A278" t="s">
         <v>30</v>
       </c>
@@ -13260,7 +13260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A279" t="s">
         <v>30</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A280" t="s">
         <v>30</v>
       </c>
@@ -13340,7 +13340,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A281" t="s">
         <v>30</v>
       </c>
@@ -13380,7 +13380,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A282" t="s">
         <v>30</v>
       </c>
@@ -13420,7 +13420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A283" t="s">
         <v>30</v>
       </c>
@@ -13460,7 +13460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A284" t="s">
         <v>30</v>
       </c>
@@ -13500,7 +13500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="285" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A285" t="s">
         <v>30</v>
       </c>
@@ -13540,7 +13540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A286" t="s">
         <v>30</v>
       </c>
@@ -13580,7 +13580,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A287" t="s">
         <v>30</v>
       </c>
@@ -13620,7 +13620,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A288" t="s">
         <v>30</v>
       </c>
@@ -13660,7 +13660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="289" spans="1:18" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>30</v>
       </c>
@@ -13700,7 +13700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A290" t="s">
         <v>30</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A291" t="s">
         <v>30</v>
       </c>
@@ -13784,7 +13784,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A292" t="s">
         <v>30</v>
       </c>
@@ -13826,7 +13826,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A293" t="s">
         <v>30</v>
       </c>
@@ -13868,7 +13868,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A294" t="s">
         <v>30</v>
       </c>
@@ -13910,7 +13910,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A295" t="s">
         <v>30</v>
       </c>
@@ -13952,7 +13952,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A296" t="s">
         <v>30</v>
       </c>
@@ -13994,7 +13994,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A297" t="s">
         <v>30</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A298" t="s">
         <v>30</v>
       </c>
@@ -14078,7 +14078,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A299" t="s">
         <v>30</v>
       </c>
@@ -14120,7 +14120,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A300" t="s">
         <v>30</v>
       </c>
@@ -14162,7 +14162,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A301" t="s">
         <v>30</v>
       </c>
@@ -14204,7 +14204,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="302" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A302" t="s">
         <v>30</v>
       </c>
@@ -14246,7 +14246,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A303" t="s">
         <v>30</v>
       </c>
@@ -14288,7 +14288,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="304" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A304" t="s">
         <v>30</v>
       </c>
@@ -14330,7 +14330,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A305" t="s">
         <v>30</v>
       </c>
@@ -14372,7 +14372,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A306" t="s">
         <v>30</v>
       </c>
@@ -14414,7 +14414,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A307" t="s">
         <v>30</v>
       </c>
@@ -14456,7 +14456,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A308" t="s">
         <v>30</v>
       </c>
@@ -14498,7 +14498,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A309" t="s">
         <v>30</v>
       </c>
@@ -14540,7 +14540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A310" t="s">
         <v>30</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A311" t="s">
         <v>30</v>
       </c>
@@ -14624,7 +14624,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A312" t="s">
         <v>30</v>
       </c>
@@ -14666,7 +14666,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A313" t="s">
         <v>30</v>
       </c>
@@ -14708,7 +14708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A314" t="s">
         <v>30</v>
       </c>
@@ -14750,7 +14750,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="315" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A315" t="s">
         <v>30</v>
       </c>
@@ -14792,7 +14792,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A316" t="s">
         <v>30</v>
       </c>
@@ -14834,7 +14834,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A317" t="s">
         <v>30</v>
       </c>
@@ -14876,7 +14876,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A318" t="s">
         <v>30</v>
       </c>
@@ -14918,7 +14918,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A319" t="s">
         <v>30</v>
       </c>
@@ -14960,7 +14960,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A320" t="s">
         <v>30</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="321" spans="1:18" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>30</v>
       </c>
@@ -17540,7 +17540,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="374" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="374" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A374" t="s">
         <v>30</v>
       </c>
@@ -17588,7 +17588,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="375" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="375" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
       <c r="A375" t="s">
         <v>30</v>
       </c>
@@ -18116,7 +18116,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="386" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="386" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A386" t="s">
         <v>30</v>
       </c>
@@ -18164,7 +18164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="387" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="387" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A387" t="s">
         <v>30</v>
       </c>
@@ -18212,7 +18212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="388" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="388" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A388" t="s">
         <v>30</v>
       </c>
@@ -18260,7 +18260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="389" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="389" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A389" t="s">
         <v>30</v>
       </c>
@@ -18308,7 +18308,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="390" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="390" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A390" t="s">
         <v>30</v>
       </c>
@@ -18356,7 +18356,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="391" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="391" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A391" t="s">
         <v>30</v>
       </c>
@@ -18404,7 +18404,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="392" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="392" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A392" t="s">
         <v>30</v>
       </c>
@@ -18452,7 +18452,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="393" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="393" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A393" t="s">
         <v>30</v>
       </c>
@@ -18500,7 +18500,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="394" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="394" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A394" t="s">
         <v>30</v>
       </c>
@@ -18548,7 +18548,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="395" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="395" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A395" t="s">
         <v>30</v>
       </c>
@@ -18596,7 +18596,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="396" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="396" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A396" t="s">
         <v>30</v>
       </c>
@@ -18644,7 +18644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="397" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="397" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A397" t="s">
         <v>30</v>
       </c>
@@ -18692,7 +18692,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="398" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="398" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A398" t="s">
         <v>30</v>
       </c>
@@ -18740,7 +18740,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="399" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="399" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A399" t="s">
         <v>30</v>
       </c>
@@ -18788,7 +18788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="400" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="400" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A400" t="s">
         <v>30</v>
       </c>
@@ -18836,7 +18836,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="401" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="401" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A401" t="s">
         <v>30</v>
       </c>
@@ -18884,7 +18884,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="402" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="402" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A402" t="s">
         <v>30</v>
       </c>
@@ -18932,7 +18932,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="403" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="403" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A403" t="s">
         <v>30</v>
       </c>
@@ -18980,7 +18980,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="404" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="404" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A404" t="s">
         <v>30</v>
       </c>
@@ -19028,7 +19028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="405" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="405" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A405" t="s">
         <v>30</v>
       </c>
@@ -19076,7 +19076,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="406" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="406" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A406" t="s">
         <v>30</v>
       </c>
@@ -19124,7 +19124,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="407" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="407" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A407" t="s">
         <v>30</v>
       </c>
@@ -19172,7 +19172,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="408" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="408" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A408" t="s">
         <v>30</v>
       </c>
@@ -19220,7 +19220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="409" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="409" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A409" t="s">
         <v>30</v>
       </c>
@@ -19268,7 +19268,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="410" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="410" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A410" t="s">
         <v>30</v>
       </c>
@@ -19364,7 +19364,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="412" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="412" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A412" t="s">
         <v>30</v>
       </c>
@@ -19412,7 +19412,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="413" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="413" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A413" t="s">
         <v>30</v>
       </c>
@@ -19460,7 +19460,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="414" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="414" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A414" t="s">
         <v>30</v>
       </c>
@@ -19508,7 +19508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="415" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="415" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A415" t="s">
         <v>30</v>
       </c>
@@ -19556,7 +19556,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="416" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="416" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A416" t="s">
         <v>30</v>
       </c>
@@ -19604,7 +19604,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="417" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="417" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A417" t="s">
         <v>30</v>
       </c>
@@ -19652,7 +19652,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="418" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="418" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A418" t="s">
         <v>30</v>
       </c>
@@ -19700,7 +19700,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="419" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="419" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A419" t="s">
         <v>30</v>
       </c>
@@ -19748,7 +19748,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="420" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="420" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A420" t="s">
         <v>30</v>
       </c>
@@ -19796,7 +19796,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="421" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="421" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A421" t="s">
         <v>30</v>
       </c>
@@ -19844,7 +19844,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="422" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="422" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A422" t="s">
         <v>30</v>
       </c>
@@ -19892,7 +19892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="423" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="423" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A423" t="s">
         <v>30</v>
       </c>
@@ -19940,7 +19940,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="424" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="424" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A424" t="s">
         <v>30</v>
       </c>
@@ -19988,7 +19988,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="425" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="425" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A425" t="s">
         <v>30</v>
       </c>
@@ -20036,7 +20036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="426" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="426" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A426" t="s">
         <v>30</v>
       </c>
@@ -20084,7 +20084,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="427" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="427" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A427" t="s">
         <v>30</v>
       </c>
@@ -20132,7 +20132,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="428" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="428" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A428" t="s">
         <v>30</v>
       </c>
@@ -20180,7 +20180,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="429" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="429" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A429" t="s">
         <v>30</v>
       </c>
@@ -20228,7 +20228,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="430" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="430" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A430" t="s">
         <v>30</v>
       </c>
@@ -20276,7 +20276,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="431" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="431" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A431" t="s">
         <v>30</v>
       </c>
@@ -20324,7 +20324,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="432" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="432" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A432" t="s">
         <v>30</v>
       </c>
@@ -20372,7 +20372,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="433" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="433" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A433" t="s">
         <v>30</v>
       </c>
@@ -20420,7 +20420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="434" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="434" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A434" t="s">
         <v>30</v>
       </c>
@@ -20468,7 +20468,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="435" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="435" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A435" t="s">
         <v>30</v>
       </c>
@@ -20516,7 +20516,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="436" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="436" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A436" t="s">
         <v>30</v>
       </c>
@@ -20564,7 +20564,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="437" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="437" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A437" t="s">
         <v>30</v>
       </c>
@@ -20612,7 +20612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="438" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="438" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A438" t="s">
         <v>30</v>
       </c>
@@ -20660,7 +20660,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="439" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="439" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A439" t="s">
         <v>30</v>
       </c>
@@ -20708,7 +20708,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="440" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="440" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A440" t="s">
         <v>30</v>
       </c>
@@ -20756,7 +20756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="441" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="441" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A441" t="s">
         <v>30</v>
       </c>
@@ -20804,7 +20804,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="442" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="442" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A442" t="s">
         <v>30</v>
       </c>
@@ -20852,7 +20852,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="443" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="443" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A443" t="s">
         <v>30</v>
       </c>
@@ -20900,7 +20900,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="444" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="444" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A444" t="s">
         <v>30</v>
       </c>
@@ -20948,7 +20948,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="445" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="445" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A445" t="s">
         <v>30</v>
       </c>
@@ -20996,7 +20996,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="446" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="446" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A446" t="s">
         <v>30</v>
       </c>
@@ -21044,7 +21044,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="447" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="447" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A447" t="s">
         <v>30</v>
       </c>
@@ -21092,7 +21092,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="448" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="448" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A448" t="s">
         <v>30</v>
       </c>
@@ -21140,7 +21140,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="449" spans="1:18" ht="17" hidden="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>30</v>
       </c>
@@ -22376,7 +22376,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="477" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="477" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A477" t="s">
         <v>31</v>
       </c>
@@ -22420,7 +22420,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="478" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="478" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A478" t="s">
         <v>31</v>
       </c>
@@ -22464,7 +22464,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="479" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="479" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A479" t="s">
         <v>31</v>
       </c>
@@ -22508,7 +22508,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="480" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="480" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A480" t="s">
         <v>31</v>
       </c>
@@ -22549,7 +22549,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="481" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="481" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A481" t="s">
         <v>31</v>
       </c>
@@ -22590,7 +22590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="482" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="482" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A482" t="s">
         <v>31</v>
       </c>
@@ -22631,7 +22631,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="483" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="483" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A483" t="s">
         <v>31</v>
       </c>
@@ -22678,7 +22678,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="484" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="484" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A484" t="s">
         <v>31</v>
       </c>
@@ -22725,7 +22725,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="485" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="485" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A485" t="s">
         <v>31</v>
       </c>
@@ -22772,7 +22772,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="486" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="486" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A486" t="s">
         <v>31</v>
       </c>
@@ -22816,7 +22816,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="487" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="487" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A487" t="s">
         <v>31</v>
       </c>
@@ -22860,7 +22860,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="488" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="488" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A488" t="s">
         <v>31</v>
       </c>
@@ -22904,7 +22904,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="489" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="489" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A489" t="s">
         <v>31</v>
       </c>
@@ -22945,7 +22945,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="490" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="490" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A490" t="s">
         <v>31</v>
       </c>
@@ -22986,7 +22986,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="491" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="491" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A491" t="s">
         <v>31</v>
       </c>
@@ -23027,7 +23027,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="492" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="492" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A492" t="s">
         <v>31</v>
       </c>
@@ -23074,7 +23074,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="493" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="493" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A493" t="s">
         <v>31</v>
       </c>
@@ -23121,7 +23121,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="494" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="494" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A494" t="s">
         <v>31</v>
       </c>
@@ -23168,7 +23168,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="495" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="495" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A495" t="s">
         <v>31</v>
       </c>
@@ -23212,7 +23212,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="496" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="496" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A496" t="s">
         <v>31</v>
       </c>
@@ -23256,7 +23256,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="497" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="497" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A497" t="s">
         <v>31</v>
       </c>
@@ -23300,7 +23300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="498" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="498" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A498" t="s">
         <v>31</v>
       </c>
@@ -23347,7 +23347,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="499" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="499" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A499" t="s">
         <v>31</v>
       </c>
@@ -23394,7 +23394,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="500" spans="1:18" hidden="1" x14ac:dyDescent="0.2">
+    <row r="500" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A500" t="s">
         <v>31</v>
       </c>
@@ -23452,9 +23452,9 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:R500" xr:uid="{AE06E5C9-F603-BD4A-AB05-F790F7B78C9A}">
-    <filterColumn colId="17">
+    <filterColumn colId="3">
       <filters>
-        <filter val="No"/>
+        <filter val="IMD"/>
       </filters>
     </filterColumn>
   </autoFilter>
